--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0022.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0022.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Vũ khí này có thể được hấp thụ để tiến hóa vũ khí khác thành Ultimate Form.</t>
+          <t>Vũ khí này có thể được hấp thụ để tiến hóa một vũ khí khác thành Hình Thái Tối Thượng.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Vũ khí này có thể được hấp thụ để tiến hóa vũ khí khác thành Ultimate Form.</t>
+          <t>Vũ khí này có thể được hấp thụ để tiến hóa một vũ khí khác thành Hình Thái Tối Thượng.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Khi những vũ khí này đạt cấp tối đa, quá trình tiến hóa thành Hình thái Tối thượng sẽ diễn ra.</t>
+          <t>Khi vũ khí đạt cấp tối đa, chúng sẽ tiến hóa thành Hình Thái Tối Thượng.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Khi những vũ khí này đạt cấp tối đa, quá trình tiến hóa thành Hình thái Tối thượng sẽ diễn ra.</t>
+          <t>Khi vũ khí đạt cấp tối đa, chúng sẽ tiến hóa thành Hình Thái Tối Thượng.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Khi những vũ khí này đạt cấp tối đa, quá trình tiến hóa thành Hình thái Tối thượng sẽ diễn ra.</t>
+          <t>Khi vũ khí đạt cấp tối đa, chúng sẽ tiến hóa thành Hình Thái Tối Thượng.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem chi tiết Tiến Hóa Vũ Khí tại đây</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết Tiến Hóa Vũ Khí tại đây.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem chi tiết Tiến Hóa Vũ Khí tại đây</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết Tiến Hóa Vũ Khí tại đây.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem chi tiết Tiến Hóa Vũ Khí tại đây</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết Tiến Hóa Vũ Khí tại đây.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Bạn có thể xem tất cả các dạng Weapon và điều kiện mở khóa tại đây</t>
+          <t>Bạn có thể xem tất cả các dạng Vũ Khí và điều kiện mở khóa tại đây</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Bạn có thể xem tất cả các dạng Weapon và điều kiện mở khóa tại đây</t>
+          <t>Bạn có thể xem tất cả các dạng Vũ Khí và điều kiện mở khóa tại đây</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Bạn có thể xem tất cả các dạng Weapon và điều kiện mở khóa tại đây</t>
+          <t>Bạn có thể xem tất cả các dạng Vũ Khí và điều kiện mở khóa tại đây</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Vật phẩm mang lại hiệu ứng thưởng đặc biệt</t>
+          <t>Vật phẩm mang lại hiệu ứng đặc biệt</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Vật phẩm mang lại hiệu ứng thưởng đặc biệt</t>
+          <t>Vật phẩm mang lại hiệu ứng đặc biệt</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Vật phẩm mang lại hiệu ứng thưởng đặc biệt</t>
+          <t>Vật phẩm mang lại hiệu ứng đặc biệt</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Rampage tặng phần thưởng bổ sung sau mỗi giai đoạn</t>
+          <t>Cuồng Nộ mang lại phần thưởng bổ sung khi kết thúc mỗi giai đoạn</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Rampage tặng phần thưởng bổ sung sau mỗi giai đoạn</t>
+          <t>Cuồng Nộ mang lại phần thưởng bổ sung khi kết thúc mỗi giai đoạn</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Rampage tặng phần thưởng bổ sung sau mỗi giai đoạn</t>
+          <t>Cuồng Nộ mang lại phần thưởng bổ sung khi kết thúc mỗi giai đoạn</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Bạn có thể mở khóa Talents tại đây để tăng cường hiệu suất của Resonator.</t>
+          <t>Tại đây, cậu có thể mở khóa Tài Năng để tăng cường hiệu suất của Resonator.</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Bạn có thể mở khóa Talents tại đây để tăng cường hiệu suất của Resonator.</t>
+          <t>Tại đây, cậu có thể mở khóa Tài Năng để tăng cường hiệu suất của Resonator.</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Bạn có thể mở khóa Talents tại đây để tăng cường hiệu suất của Resonator.</t>
+          <t>Tại đây, cậu có thể mở khóa Tài Năng để tăng cường hiệu suất của Resonator.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Boost hiệu suất cho Resonator tại đây</t>
+          <t>Tăng cường hiệu suất Resonator tại đây</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Boost hiệu suất cho Resonator tại đây</t>
+          <t>Tăng cường hiệu suất Resonator tại đây</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Boost hiệu suất cho Resonator tại đây</t>
+          <t>Tăng cường hiệu suất Resonator tại đây</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Bạn có thể kích hoạt Chế độ Helltide để tăng độ khắc nghiệt cho các mũi khoan</t>
+          <t>Cậu có thể kích hoạt Chế Độ Helltide để tăng độ khó cho buổi luyện tập.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Bạn có thể kích hoạt Chế độ Helltide để tăng độ khắc nghiệt cho các mũi khoan</t>
+          <t>Cậu có thể kích hoạt Chế Độ Helltide để tăng độ khó cho buổi luyện tập.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Bạn có thể kích hoạt Chế độ Helltide để tăng độ khắc nghiệt cho các mũi khoan</t>
+          <t>Cậu có thể kích hoạt Chế Độ Helltide để tăng độ khó cho buổi luyện tập.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Weapons mở khóa hiệu ứng Tiến Hóa sau khi đạt cấp nhất định</t>
+          <t>Vũ khí mở khóa hiệu ứng Tiến Hóa khi đạt cấp độ nhất định.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Weapons mở khóa hiệu ứng Tiến Hóa sau khi đạt cấp nhất định</t>
+          <t>Vũ khí mở khóa hiệu ứng Tiến Hóa khi đạt cấp độ nhất định.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Weapons mở khóa hiệu ứng Tiến Hóa sau khi đạt cấp nhất định</t>
+          <t>Vũ khí mở khóa hiệu ứng Tiến Hóa khi đạt cấp độ nhất định.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Để hoàn thành mục tiêu chụp ảnh, bạn cần chụp &lt;color=#8c7e51&gt;Resonator yêu cầu&lt;/color&gt; thực hiện &lt;color=#8c7e51&gt;hành động chỉ định&lt;/color&gt;</t>
+          <t>Để hoàn thành mục tiêu chụp ảnh, cậu cần chụp &lt;color=#8c7e51&gt;Resonator được yêu cầu&lt;/color&gt; thực hiện &lt;color=#8c7e51&gt;hành động chỉ định&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Để hoàn thành mục tiêu chụp ảnh, bạn cần chụp &lt;color=#8c7e51&gt;Resonator yêu cầu&lt;/color&gt; thực hiện &lt;color=#8c7e51&gt;hành động chỉ định&lt;/color&gt;</t>
+          <t>Để hoàn thành mục tiêu chụp ảnh, cậu cần chụp &lt;color=#8c7e51&gt;Resonator được yêu cầu&lt;/color&gt; thực hiện &lt;color=#8c7e51&gt;hành động chỉ định&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Để hoàn thành mục tiêu chụp ảnh, bạn cần chụp &lt;color=#8c7e51&gt;Resonator yêu cầu&lt;/color&gt; thực hiện &lt;color=#8c7e51&gt;hành động chỉ định&lt;/color&gt;</t>
+          <t>Để hoàn thành mục tiêu chụp ảnh, cậu cần chụp &lt;color=#8c7e51&gt;Resonator được yêu cầu&lt;/color&gt; thực hiện &lt;color=#8c7e51&gt;hành động chỉ định&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Bạn có thể tùy chỉnh đội hình, nhưng phải chọn Resonator yêu cầu nếu chưa hoàn thành mục tiêu.</t>
+          <t>Bạn có thể sắp xếp đội hình, nhưng phải chọn Resonator bắt buộc nếu chưa hoàn thành mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Bạn có thể tùy chỉnh đội hình, nhưng phải chọn Resonator yêu cầu nếu chưa hoàn thành mục tiêu.</t>
+          <t>Bạn có thể sắp xếp đội hình, nhưng phải chọn Resonator bắt buộc nếu chưa hoàn thành mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Bạn có thể tùy chỉnh đội hình, nhưng phải chọn Resonator yêu cầu nếu chưa hoàn thành mục tiêu.</t>
+          <t>Bạn có thể sắp xếp đội hình, nhưng phải chọn Resonator bắt buộc nếu chưa hoàn thành mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Trong hành động chỉ định, khung chụp sẽ xuất hiện trên màn hình</t>
+          <t>Trong quá trình hành động chỉ định, khung bắt mục tiêu sẽ xuất hiện trên màn hình.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Trong hành động chỉ định, khung chụp sẽ xuất hiện trên màn hình</t>
+          <t>Trong quá trình hành động chỉ định, khung bắt mục tiêu sẽ xuất hiện trên màn hình.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Trong hành động chỉ định, khung chụp sẽ xuất hiện trên màn hình</t>
+          <t>Trong quá trình hành động chỉ định, khung bắt mục tiêu sẽ xuất hiện trên màn hình.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Đã đạt yêu cầu mục tiêu, sử dụng Freeze Frame Camera ngay</t>
+          <t>Đã đạt yêu cầu nhiệm vụ, có thể sử dụng Máy Ảnh Tạm Dừng ngay</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Đã đạt yêu cầu mục tiêu, sử dụng Freeze Frame Camera ngay</t>
+          <t>Đã đạt yêu cầu nhiệm vụ, có thể sử dụng Máy Ảnh Tạm Dừng ngay</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Xem mục tiêu chụp ảnh tại đây</t>
+          <t>Bạn có thể xem mục tiêu chụp ảnh tại đây</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Xem mục tiêu chụp ảnh tại đây</t>
+          <t>Bạn có thể xem mục tiêu chụp ảnh tại đây</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Xem mục tiêu chụp ảnh tại đây</t>
+          <t>Bạn có thể xem mục tiêu chụp ảnh tại đây</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn hiệu ứng Filter tại đây</t>
+          <t>Cậu có thể chọn hiệu ứng Lọc ở đây.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn hiệu ứng Filter tại đây</t>
+          <t>Cậu có thể chọn hiệu ứng Lọc ở đây.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn hiệu ứng Filter tại đây</t>
+          <t>Cậu có thể chọn hiệu ứng Lọc ở đây.</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Bạn có thể bật/tắt Ẩn Kẻ Địch tại đây</t>
+          <t>Cậu có thể bật/tắt Ẩn Kẻ Địch ở đây</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{0} Bạn có thể bật/tắt Ẩn Kẻ Địch tại đây</t>
+          <t>{0} Cậu có thể bật/tắt Ẩn kẻ địch tại đây</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Bạn có thể bật/tắt Ẩn Kẻ Địch tại đây</t>
+          <t>Cậu có thể bật/tắt Ẩn Kẻ Địch ở đây</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Điều chỉnh góc máy và chụp lại khoảnh khắc Resonator đang hành động để hoàn thành mục tiêu</t>
+          <t>Điều chỉnh camera và ghi lại khoảnh khắc Resonator thực hiện kỹ năng để hoàn thành mục tiêu</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Điều chỉnh góc máy và chụp lại khoảnh khắc Resonator đang hành động để hoàn thành mục tiêu</t>
+          <t>Điều chỉnh camera và ghi lại khoảnh khắc Resonator thực hiện kỹ năng để hoàn thành mục tiêu</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Điều chỉnh góc máy và chụp lại khoảnh khắc Resonator đang hành động để hoàn thành mục tiêu</t>
+          <t>Điều chỉnh camera và ghi lại khoảnh khắc Resonator thực hiện kỹ năng để hoàn thành mục tiêu</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Sau khi hoàn thành mục tiêu, bạn có thể quay lại khu vực và chụp ảnh với bất kỳ Resonator nào</t>
+          <t>Sau khi hoàn thành mục tiêu, cậu có thể quay lại sân khấu và chụp ảnh với bất kỳ Resonator nào.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Sau khi hoàn thành mục tiêu, bạn có thể quay lại khu vực và chụp ảnh với bất kỳ Resonator nào</t>
+          <t>Sau khi hoàn thành mục tiêu, cậu có thể quay lại sân khấu và chụp ảnh với bất kỳ Resonator nào.</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Sau khi hoàn thành mục tiêu, bạn có thể quay lại khu vực và chụp ảnh với bất kỳ Resonator nào</t>
+          <t>Sau khi hoàn thành mục tiêu, cậu có thể quay lại sân khấu và chụp ảnh với bất kỳ Resonator nào.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Ở Chế độ Khó, bạn có thể dùng vật phẩm Làm Chậm Thời Gian bất cứ lúc nào để làm chậm thời gian</t>
+          <t>Ở Chế Độ Khó, ngươi có thể sử dụng thiết bị Chế Độ Chậm bất cứ lúc nào để làm chậm thời gian.</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Ở Chế độ Khó, bạn có thể dùng vật phẩm Làm Chậm Thời Gian bất cứ lúc nào để làm chậm thời gian</t>
+          <t>Ở Chế Độ Khó, ngươi có thể sử dụng thiết bị Chế Độ Chậm bất cứ lúc nào để làm chậm thời gian.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Ở Chế độ Khó, bạn có thể dùng vật phẩm Làm Chậm Thời Gian bất cứ lúc nào để làm chậm thời gian</t>
+          <t>Ở Chế Độ Khó, ngươi có thể sử dụng thiết bị Chế Độ Chậm bất cứ lúc nào để làm chậm thời gian.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Namipon Stickers mạnh hơn sẽ được trang bị tự động khi nhặt lên.</t>
+          <t>Các miếng dán Namipon mạnh hơn sẽ tự động được trang bị khi nhặt lên.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Namipon Stickers mạnh hơn sẽ được trang bị tự động khi nhặt lên.</t>
+          <t>Các miếng dán Namipon mạnh hơn sẽ tự động được trang bị khi nhặt lên.</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Namipon Stickers mạnh hơn sẽ được trang bị tự động khi nhặt lên.</t>
+          <t>Các miếng dán Namipon mạnh hơn sẽ tự động được trang bị khi nhặt lên.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Một số vật phẩm chiến lợi phẩm có thể được bán từ Warehouse.</t>
+          <t>Một số vật phẩm chiến lợi phẩm có thể bán từ Kho hàng.</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Một số vật phẩm chiến lợi phẩm có thể được bán từ Warehouse.</t>
+          <t>Một số vật phẩm chiến lợi phẩm có thể bán từ Kho hàng.</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Một số vật phẩm chiến lợi phẩm có thể được bán từ Warehouse.</t>
+          <t>Một số vật phẩm chiến lợi phẩm có thể bán từ Kho hàng.</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Dùng Bánh Dango để mở khóa thêm ô Sticker.</t>
+          <t>Dùng Bánh Dango Gạo để mở thêm ô Dán Hình.</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Dùng Bánh Dango để mở khóa thêm ô Sticker.</t>
+          <t>Dùng Bánh Dango Gạo để mở thêm ô Dán Hình.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Dùng Bánh Dango để mở khóa thêm ô Sticker.</t>
+          <t>Dùng Bánh Dango Gạo để mở thêm ô Dán Hình.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Vật phẩm nhặt được trong quá trình khám phá có thể bán lấy Bánh Rice Dango.</t>
+          <t>Vật phẩm thu thập được trong quá trình khám phá có thể bán lấy Bánh Gạo Dango.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Vật phẩm nhặt được trong quá trình khám phá có thể bán lấy Bánh Rice Dango.</t>
+          <t>Vật phẩm thu thập được trong quá trình khám phá có thể bán lấy Bánh Gạo Dango.</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Vật phẩm nhặt được trong quá trình khám phá có thể bán lấy Bánh Rice Dango.</t>
+          <t>Vật phẩm thu thập được trong quá trình khám phá có thể bán lấy Bánh Gạo Dango.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Chọn tất cả vật phẩm chiến lợi phẩm không thể trang bị.</t>
+          <t>Chọn tất cả các vật phẩm không thể trang bị.</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Chọn tất cả vật phẩm chiến lợi phẩm không thể trang bị.</t>
+          <t>Chọn tất cả các vật phẩm không thể trang bị.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Chọn tất cả vật phẩm chiến lợi phẩm không thể trang bị.</t>
+          <t>Chọn tất cả các vật phẩm không thể trang bị.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Sell tất cả vật phẩm không trang bị được để lấy Rice Dango.</t>
+          <t>Bán toàn bộ vật phẩm không trang bị được để lấy Bánh Gạo Dango.</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Sell tất cả vật phẩm không trang bị được để lấy Rice Dango.</t>
+          <t>Bán toàn bộ vật phẩm không trang bị được để lấy Bánh Gạo Dango.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Sell tất cả vật phẩm không trang bị được để lấy Rice Dango.</t>
+          <t>Bán toàn bộ vật phẩm không trang bị được để lấy Bánh Gạo Dango.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Chọn ô bị khóa và tiêu hao Bánh Rice Dango để mở khóa.</t>
+          <t>Chọn ô bị khóa và tiêu Bánh Dango Gạo để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Chọn ô bị khóa và tiêu hao Bánh Rice Dango để mở khóa.</t>
+          <t>Chọn ô bị khóa và tiêu Bánh Dango Gạo để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Chọn ô bị khóa và tiêu hao Bánh Rice Dango để mở khóa.</t>
+          <t>Chọn ô bị khóa và tiêu Bánh Dango Gạo để mở khóa.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Kẻ địch sẽ trở nên mạnh hơn theo thời gian. Hãy chú ý thời gian và đảm bảo an toàn khi khám phá Honami City!</t>
+          <t>Kẻ địch sẽ trở nên mạnh hơn theo thời gian. Hãy để ý thời gian và cẩn thận khi khám phá Thành phố Honami!</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>{0}+{1} Kẻ địch sẽ trở nên mạnh hơn theo thời gian. Hãy chú ý thời gian và đảm bảo an toàn khi khám phá Honami City!</t>
+          <t>{0}+{1} Kẻ địch sẽ trở nên mạnh hơn theo thời gian. Hãy chú ý thời gian và đảm bảo an toàn khi khám phá Thành Phố Honami!</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Kẻ địch sẽ trở nên mạnh hơn theo thời gian. Hãy chú ý thời gian và đảm bảo an toàn khi khám phá Honami City!</t>
+          <t>Kẻ địch sẽ trở nên mạnh hơn theo thời gian. Hãy để ý thời gian và cẩn thận khi khám phá Thành phố Honami!</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Nâng cấp Namipon Badge sẽ tăng Độ Stability Tối Đa.</t>
+          <t>Nâng cấp Huy hiệu Namipon sẽ tăng Giới hạn Ổn định tối đa.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>{0} Nâng cấp Namipon Badge làm tăng Độ Stability Tối Đa.</t>
+          <t>{0} Nâng cấp Huy Hiệu Namipon sẽ tăng Độ Ổn Định tối đa.</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Nâng cấp Namipon Badge sẽ tăng Độ Stability Tối Đa.</t>
+          <t>Nâng cấp Huy hiệu Namipon sẽ tăng Giới hạn Ổn định tối đa.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Sau khi đặt vé Namipon Shuttle, {Cus:Ipt,Touch=tap PC=bấm Gamepad=press} vào đây để Extract.</t>
+          <t>Sau khi đặt vé tàu con thoi Namipon, {Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để Trích Xuất.</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>{0} Sau khi đặt vé tàu Namipon, {Cus:Ipt,Touch=tap PC=bấm Gamepad=press} vào đây để Trích Xuất.</t>
+          <t>Sau khi đặt vé tàu Namipon, {Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để Trích Xuất.</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Sau khi đặt vé Namipon Shuttle, {Cus:Ipt,Touch=tap PC=bấm Gamepad=press} vào đây để Extract.</t>
+          <t>Sau khi đặt vé tàu con thoi Namipon, {Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để Trích Xuất.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Một số vật phẩm chiến lợi phẩm có thể được bán từ Warehouse.</t>
+          <t>Một số vật phẩm chiến lợi phẩm có thể bán từ Kho hàng.</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Một số vật phẩm chiến lợi phẩm có thể được bán từ Warehouse.</t>
+          <t>Một số vật phẩm chiến lợi phẩm có thể bán từ Kho hàng.</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Một số vật phẩm chiến lợi phẩm có thể được bán từ Warehouse.</t>
+          <t>Một số vật phẩm chiến lợi phẩm có thể bán từ Kho hàng.</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>{0} Hình Dán Namipon bạn thu thập đã được thêm vào Storage Bag.</t>
+          <t>{0} Các sticker Namipon cậu sưu tầm đã được thêm vào Túi Lưu Trữ.</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Giữ&lt;/color&gt; {0} để mở &lt;color=#ffd12f&gt;Storage Bag&lt;/color&gt; qua menu tròn và xem các Sticker đã thu thập.</t>
+          <t>Giữ &lt;color=#ffd12f&gt;{0}&lt;/color&gt; để mở &lt;color=#ffd12f&gt;Túi Đồ&lt;/color&gt; qua vòng điều hướng và xem các Sticker đã thu thập</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Những tấm sticker Namipon bạn thu thập đã được thêm vào Storage Bag.</t>
+          <t>Các sticker Namipon cậu thu thập đã được thêm vào Túi Lưu Trữ.</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Equip Sticker để tăng sức chiến đấu cho Resonators.</t>
+          <t>Dán Sticker để tăng sức mạnh chiến đấu cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>{0} Equip Hình Dán để tăng sức chiến đấu của Resonators.</t>
+          <t>{0} Trang bị Hình Dán để tăng sức chiến đấu cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Equip Sticker để tăng sức chiến đấu cho Resonators.</t>
+          <t>Dán Sticker để tăng sức mạnh chiến đấu cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Bạn có thể trang bị nhanh Sticker.</t>
+          <t>Bạn có thể trang bị nhanh các Sticker.</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>{0} Bạn can quick-equip Stickers.</t>
+          <t>{0} Cậu có thể gắn Sticker nhanh chóng.</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Bạn có thể trang bị nhanh Sticker.</t>
+          <t>Bạn có thể trang bị nhanh các Sticker.</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Khi Stability giảm về 0, bạn sẽ mất khả năng chiến đấu và cuộc thám hiểm hiện tại sẽ tự động kết thúc.</t>
+          <t>Khi Độ Ổn Định giảm về 0, cậu sẽ mất khả năng chiến đấu và cuộc thám hiểm sẽ tự động kết thúc.</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Khi Stability giảm về 0, bạn sẽ mất khả năng chiến đấu và cuộc thám hiểm hiện tại sẽ tự động kết thúc.</t>
+          <t>Khi Độ Ổn Định giảm về 0, cậu sẽ mất khả năng chiến đấu và cuộc thám hiểm sẽ tự động kết thúc.</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Khi Stability giảm về 0, bạn sẽ mất khả năng chiến đấu và cuộc thám hiểm hiện tại sẽ tự động kết thúc.</t>
+          <t>Khi Độ Ổn Định giảm về 0, cậu sẽ mất khả năng chiến đấu và cuộc thám hiểm sẽ tự động kết thúc.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Namipon Badge có thể tăng Độ Stability Tối Đa.</t>
+          <t>Huy Hiệu Namipon có thể tăng Độ Ổn Định Tối Đa.</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Namipon Badge có thể tăng Độ Stability Tối Đa.</t>
+          <t>Huy Hiệu Namipon có thể tăng Độ Ổn Định Tối Đa.</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Namipon Badge có thể tăng Độ Stability Tối Đa.</t>
+          <t>Huy Hiệu Namipon có thể tăng Độ Ổn Định Tối Đa.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn một Namipon hỗ trợ để đồng hành trong các chuyến khám phá. Ghép chúng với các Hình Dán có hình dạng cụ thể để kích hoạt thưởng.</t>
+          <t>Cậu có thể chọn một Namipon hỗ trợ để đồng hành trong chuyến thám hiểm. Ghép chúng với các Hình dán có hình dạng phù hợp để kích hoạt thêm bonus.</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn một Namipon hỗ trợ để đồng hành trong các chuyến khám phá. Ghép chúng với các Hình Dán có hình dạng cụ thể để kích hoạt thưởng.</t>
+          <t>Cậu có thể chọn một Namipon hỗ trợ để đồng hành trong chuyến thám hiểm. Ghép chúng với các Hình dán có hình dạng phù hợp để kích hoạt thêm bonus.</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Bạn có thể chọn một Namipon hỗ trợ để đồng hành trong các chuyến khám phá. Ghép chúng với các Hình Dán có hình dạng cụ thể để kích hoạt thưởng.</t>
+          <t>Cậu có thể chọn một Namipon hỗ trợ để đồng hành trong chuyến thám hiểm. Ghép chúng với các Hình dán có hình dạng phù hợp để kích hoạt thêm bonus.</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để nhanh chóng đặt Sticker vào các ô thích hợp.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để đặt nhanh Sticker vào các ô tương ứng</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để đặt Sticker nhanh vào các ô phù hợp.</t>
+          <t>{0} {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để đặt nhanh Sticker vào các ô tương ứng.</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để nhanh chóng đặt Sticker vào các ô thích hợp.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để đặt nhanh Sticker vào các ô tương ứng</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem hiệu ứng Kỹ Năng Hỗ Trợ.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hiệu ứng Kỹ Năng Hỗ Trợ.</t>
         </is>
       </c>
     </row>
@@ -8114,7 +8114,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem hiệu ứng Kỹ Năng Hỗ Trợ.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hiệu ứng Kỹ Năng Hỗ Trợ.</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem hiệu ứng Kỹ Năng Hỗ Trợ.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem hiệu ứng Kỹ Năng Hỗ Trợ.</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Hoàn thành bộ Sticker để nhận hỗ trợ tăng cường từ Namipons</t>
+          <t>Hoàn thành bộ Sticker để nhận hỗ trợ tăng cường từ Namipon.</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Hoàn thành bộ Sticker để nhận hỗ trợ tăng cường từ Namipons</t>
+          <t>Hoàn thành bộ Sticker để nhận hỗ trợ tăng cường từ Namipon.</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Hoàn thành bộ Sticker để nhận hỗ trợ tăng cường từ Namipons</t>
+          <t>Hoàn thành bộ Sticker để nhận hỗ trợ tăng cường từ Namipon.</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>{0} Dùng Kỹ Năng Hỗ Trợ để triệu hồi Namipon trợ giúp.</t>
+          <t>Sử dụng Kỹ Năng Hỗ Trợ để triệu hồi Namipon trợ giúp cậu.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>{0} Dùng Kỹ Năng Hỗ Trợ để triệu hồi Namipon trợ giúp.</t>
+          <t>Sử dụng Kỹ Năng Hỗ Trợ để triệu hồi Namipon trợ giúp cậu.</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Nâng cấp Trang Trí Quán Cà Phê sẽ mang lại nhiều lợi ích khác nhau trong quá trình khám phá.</t>
+          <t>Nâng cấp Trang trí Quán Cà phê sẽ mang lại nhiều đặc quyền hữu ích trong hành trình khám phá của cậu.</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Nâng cấp Trang Trí Quán Cà Phê sẽ mang lại nhiều lợi ích khác nhau trong quá trình khám phá.</t>
+          <t>Nâng cấp Trang trí Quán Cà phê sẽ mang lại nhiều đặc quyền hữu ích trong hành trình khám phá của cậu.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Nâng cấp Trang Trí Quán Cà Phê sẽ mang lại nhiều lợi ích khác nhau trong quá trình khám phá.</t>
+          <t>Nâng cấp Trang trí Quán Cà phê sẽ mang lại nhiều đặc quyền hữu ích trong hành trình khám phá của cậu.</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Bạn có thể khám phá khu vực tiếp theo ngay bây giờ.</t>
+          <t>Giờ cậu có thể khám phá khu vực tiếp theo rồi.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>{0} Bạn có thể khám phá khu vực tiếp theo.</t>
+          <t>{0} Cậu có thể khám phá khu vực tiếp theo ngay bây giờ.</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Bạn có thể khám phá khu vực tiếp theo ngay bây giờ.</t>
+          <t>Giờ cậu có thể khám phá khu vực tiếp theo rồi.</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Kích hoạt Namipon Lightbox sẽ tiết lộ kẻ địch và Rương Vật Phẩm xung quanh.</t>
+          <t>Kích hoạt Namipon Lightbox sẽ phát hiện kẻ địch và Rương Vật Tư trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Kích hoạt Namipon Lightbox sẽ tiết lộ kẻ địch và Rương Vật Phẩm xung quanh.</t>
+          <t>Kích hoạt Namipon Lightbox sẽ phát hiện kẻ địch và Rương Vật Tư trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Kích hoạt Namipon Lightbox sẽ tiết lộ kẻ địch và Rương Vật Phẩm xung quanh.</t>
+          <t>Kích hoạt Namipon Lightbox sẽ phát hiện kẻ địch và Rương Vật Tư trong phạm vi.</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Tìm Namipon bị lạc ở Honami City để nhận thưởng.</t>
+          <t>Tìm những Namipon bị lạc ở Thành phố Honami để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Tìm Namipon bị lạc ở Honami City để nhận thưởng.</t>
+          <t>Tìm những Namipon bị lạc ở Thành phố Honami để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Tìm Namipon bị lạc ở Honami City để nhận thưởng.</t>
+          <t>Tìm những Namipon bị lạc ở Thành phố Honami để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Đánh dấu để tiêu hao Bánh Rice Dango, cho phép bạn Trích Xuất bất cứ lúc nào.</t>
+          <t>Bấm vào đây để dùng Bánh Gạo Dango, cho phép cậu Giải Trích bất cứ lúc nào.</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Đánh dấu {0} để tiêu hao Bánh Rice Dango, cho phép bạn Trích Xuất bất cứ lúc nào.</t>
+          <t>{0} Đánh dấu để tiêu Gạo Dango, cho phép Trích Xuất bất cứ lúc nào.</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Đánh dấu để tiêu hao Bánh Rice Dango, cho phép bạn Trích Xuất bất cứ lúc nào.</t>
+          <t>Bấm vào đây để dùng Bánh Gạo Dango, cho phép cậu Giải Trích bất cứ lúc nào.</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} vào đây để di chuyển đến Neon Tower và bắt đầu thử thách.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để đến Tháp Neon và bắt đầu thử thách.</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để di chuyển đến Neon Tower và bắt đầu thử thách.</t>
+          <t>{0} {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để di chuyển đến Tháp Neon và bắt đầu thử thách.</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} vào đây để di chuyển đến Neon Tower và bắt đầu thử thách.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để đến Tháp Neon và bắt đầu thử thách.</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Bạn có thể khởi hành khi đã sẵn sàng.</t>
+          <t>Bạn có thể lên đường khi đã sẵn sàng.</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Bạn có thể khởi hành khi đã sẵn sàng.</t>
+          <t>Bạn có thể lên đường khi đã sẵn sàng.</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Bạn có thể khởi hành khi đã sẵn sàng.</t>
+          <t>Bạn có thể lên đường khi đã sẵn sàng.</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Inspect những Namipon hỗ trợ mới mở khóa của bạn tại đây.</t>
+          <t>Kiểm tra các Namipon hỗ trợ mới mở khóa của cậu ở đây</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Inspect những Namipon hỗ trợ mới mở khóa của bạn tại đây.</t>
+          <t>Kiểm tra các Namipon hỗ trợ mới mở khóa của cậu ở đây</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Inspect những Namipon hỗ trợ mới mở khóa của bạn tại đây.</t>
+          <t>Kiểm tra các Namipon hỗ trợ mới mở khóa của cậu ở đây</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để kiểm tra hoặc đổi Namipon hỗ trợ.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để kiểm tra hoặc đổi Namipon hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để kiểm tra hoặc đổi Namipon hỗ trợ.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để kiểm tra hoặc đổi Namipon hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để kiểm tra hoặc đổi Namipon hỗ trợ.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để kiểm tra hoặc đổi Namipon hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Bạn có thể xem thông tin hỗ trợ Namipon tại đây.</t>
+          <t>Bạn có thể xem chi tiết hỗ trợ Namipon tại đây</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Bạn có thể xem thông tin hỗ trợ Namipon tại đây.</t>
+          <t>Bạn có thể xem chi tiết hỗ trợ Namipon tại đây</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Bạn có thể xem thông tin hỗ trợ Namipon tại đây.</t>
+          <t>Bạn có thể xem chi tiết hỗ trợ Namipon tại đây</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Bạn có thể chuẩn bị Namipon hỗ trợ này để triển khai.</t>
+          <t>Bạn có thể chuẩn bị triển khai Namipon hỗ trợ này.</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Bạn có thể chuẩn bị Namipon hỗ trợ này để triển khai.</t>
+          <t>Bạn có thể chuẩn bị triển khai Namipon hỗ trợ này.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Bạn có thể chuẩn bị Namipon hỗ trợ này để triển khai.</t>
+          <t>Bạn có thể chuẩn bị triển khai Namipon hỗ trợ này.</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Bạn có thể Extract an toàn sau khi hoàn thành Mục tiêu Main.</t>
+          <t>Sau khi hoàn thành Mục Tiêu Chính, ngươi có thể An Toàn Rút lui.</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Bạn có thể Extract an toàn sau khi hoàn thành Mục tiêu Main.</t>
+          <t>Sau khi hoàn thành Mục Tiêu Chính, ngươi có thể An Toàn Rút lui.</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Bạn có thể Extract an toàn sau khi hoàn thành Mục tiêu Main.</t>
+          <t>Sau khi hoàn thành Mục Tiêu Chính, ngươi có thể An Toàn Rút lui.</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Hoàn thành Mục tiêu Phụ để nhận thêm phần thưởng.</t>
+          <t>Hoàn thành Mục Tiêu Phụ để nhận thêm phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Hoàn thành Mục tiêu Phụ để nhận thêm phần thưởng.</t>
+          <t>Hoàn thành Mục Tiêu Phụ để nhận thêm phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Hoàn thành Mục tiêu Phụ để nhận thêm phần thưởng.</t>
+          <t>Hoàn thành Mục Tiêu Phụ để nhận thêm phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Cấp độ chiến đấu của Resonators và kẻ địch được hiển thị tại đây. Hãy lưu ý khoảng cách cấp độ khi khám phá.</t>
+          <t>Mức độ chiến đấu của Resonator và kẻ địch được hiển thị tại đây. Hãy lưu ý khoảng cách cấp độ khi khám phá nhé.</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Cấp độ chiến đấu của Resonators và kẻ địch được hiển thị tại đây. Hãy lưu ý khoảng cách cấp độ khi khám phá.</t>
+          <t>Mức độ chiến đấu của Resonator và kẻ địch được hiển thị tại đây. Hãy lưu ý khoảng cách cấp độ khi khám phá nhé.</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Cấp độ chiến đấu của Resonators và kẻ địch được hiển thị tại đây. Hãy lưu ý khoảng cách cấp độ khi khám phá.</t>
+          <t>Mức độ chiến đấu của Resonator và kẻ địch được hiển thị tại đây. Hãy lưu ý khoảng cách cấp độ khi khám phá nhé.</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>{0} {Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem Mục Tiêu Main và Side Objectives.</t>
+          <t>Nhấn {0} để xem Nhiệm Vụ Chính và Nhiệm Vụ Phụ</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Giữ &lt;/color&gt; {0} và chọn &lt;color=#ffd12f&gt;Quests&lt;/color&gt; trên vòng tròn để xem Mục tiêu chính và Mục tiêu phụ.</t>
+          <t>Giữ {0} và chọn &lt;color=#ffd12f&gt;Nhiệm Vụ&lt;/color&gt; từ bánh xe lệnh để xem Mục Tiêu Chính và Mục Tiêu Phụ.</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} để xem chi tiết Nhiệm Vụ Main và Side Objectives.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết Nhiệm Vụ Chính và Nhiệm Vụ Phụ.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Theo dõi tiến độ thu thập Namipon bị thất lạc tại đây.</t>
+          <t>Theo dõi tiến độ thu thập Namipon thất lạc tại đây.</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Theo dõi tiến độ thu thập Namipon bị thất lạc tại đây.</t>
+          <t>Theo dõi tiến độ thu thập Namipon thất lạc tại đây.</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Theo dõi tiến độ thu thập Namipon bị thất lạc tại đây.</t>
+          <t>Theo dõi tiến độ thu thập Namipon thất lạc tại đây.</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Có thể mua vật tư từ Sales Champ.</t>
+          <t>Vật tư có thể mua từ Nhân viên Bán hàng.</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12209,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Có thể mua vật tư từ Sales Champ.</t>
+          <t>Vật tư có thể mua từ Nhân viên Bán hàng.</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Có thể mua vật tư từ Sales Champ.</t>
+          <t>Vật tư có thể mua từ Nhân viên Bán hàng.</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Dùng Bánh Rice Dango để nâng cấp Namipon Badge.</t>
+          <t>Dùng Bánh Dango Gạo để nâng cấp Huy Hiệu Namipon.</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Dùng Bánh Rice Dango để nâng cấp Namipon Badge.</t>
+          <t>Dùng Bánh Dango Gạo để nâng cấp Huy Hiệu Namipon.</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12469,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Dùng Bánh Rice Dango để nâng cấp Namipon Badge.</t>
+          <t>Dùng Bánh Dango Gạo để nâng cấp Huy Hiệu Namipon.</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Nâng cấp Trang Trí Quán Cà Phê để mở khóa Hồ Sơ Namipon.</t>
+          <t>Nâng cấp Trang trí Quán cà phê để mở khóa tập tin bí ẩn Namipon.</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Nâng cấp Trang Trí Quán Cà Phê để mở khóa Hồ Sơ Namipon.</t>
+          <t>Nâng cấp Trang trí Quán cà phê để mở khóa tập tin bí ẩn Namipon.</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Nâng cấp Trang Trí Quán Cà Phê để mở khóa Hồ Sơ Namipon.</t>
+          <t>Nâng cấp Trang trí Quán cà phê để mở khóa tập tin bí ẩn Namipon.</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Equip Namipon Stickers để tăng Combat Power.</t>
+          <t>Dán Sticker Namipon để tăng Sức Mạnh Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -12989,7 +12989,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Equip Namipon Stickers để tăng Combat Power.</t>
+          <t>Dán Sticker Namipon để tăng Sức Mạnh Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Equip Namipon Stickers để tăng Combat Power.</t>
+          <t>Dán Sticker Namipon để tăng Sức Mạnh Chiến Đấu.</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Equip Sticker độc quyền của Resonator để nhận hiệu ứng mạnh mẽ.</t>
+          <t>Trang bị Hình Dán độc quyền của Resonator để nhận hiệu ứng mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>{0} Equip Sticker độc quyền của Resonator để nhận hiệu ứng mạnh mẽ.</t>
+          <t>{0} Trang bị Hình Dán độc quyền của Resonator để nhận hiệu ứng mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Equip Sticker độc quyền của Resonator để nhận hiệu ứng mạnh mẽ.</t>
+          <t>Trang bị Hình Dán độc quyền của Resonator để nhận hiệu ứng mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Namipon Sticker này chỉ áp dụng cho Rover, tăng cường đáng kể sức chiến đấu của Rover.</t>
+          <t>Hiệu ứng của miếng dán Namipon này chỉ áp dụng cho Rover, tăng cường đáng kể sức chiến đấu của Rover.</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Namipon Sticker này chỉ áp dụng cho Rover, tăng cường đáng kể sức chiến đấu của Rover.</t>
+          <t>Hiệu ứng của miếng dán Namipon này chỉ áp dụng cho Rover, tăng cường đáng kể sức chiến đấu của Rover.</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Hiệu ứng của Namipon Sticker này chỉ áp dụng cho Rover, tăng cường đáng kể sức chiến đấu của Rover.</t>
+          <t>Hiệu ứng của miếng dán Namipon này chỉ áp dụng cho Rover, tăng cường đáng kể sức chiến đấu của Rover.</t>
         </is>
       </c>
     </row>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để rời đi an toàn và giữ lại tất cả chiến lợi phẩm.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để rời đi an toàn và giữ lại toàn bộ chiến lợi phẩm.</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để rời đi an toàn và giữ lại tất cả chiến lợi phẩm.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để rời đi an toàn và giữ lại toàn bộ chiến lợi phẩm.</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} để rời đi an toàn và giữ lại tất cả chiến lợi phẩm.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để rời đi an toàn và giữ lại toàn bộ chiến lợi phẩm.</t>
         </is>
       </c>
     </row>
@@ -13704,7 +13704,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Bạn đã nhận được một Resonator Sticker. Nó đã được thêm vào Túi đồ.</t>
+          <t>Bạn đã nhận được một Hình Dán Resonator. Nó đã được thêm vào Túi Lưu Trữ của bạn.</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13769,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Giữ &lt;/color&gt; {0} và chọn &lt;color=#ffd12f&gt;Storage Bag&lt;/color&gt; trên vòng tròn để xem các Sticker Resonator đặc biệt bạn đã thu thập.</t>
+          <t>Giữ {0} và chọn &lt;color=#ffd12f&gt;Túi Lưu Trữ&lt;/color&gt; từ bánh xe lệnh để xem các Sticker Resonator mà ngươi đã thu thập.</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Bạn đã nhận được một Resonator Sticker. Nó đã được thêm vào Túi đồ.</t>
+          <t>Bạn đã nhận được một Hình Dán Resonator. Nó đã được thêm vào Túi Lưu Trữ của bạn.</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Dùng Bánh Rice Dango để nâng cấp Namipon Badge.</t>
+          <t>Dùng Bánh Dango Gạo để nâng cấp Huy Hiệu Namipon.</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Dùng Bánh Rice Dango để nâng cấp Namipon Badge.</t>
+          <t>Dùng Bánh Dango Gạo để nâng cấp Huy Hiệu Namipon.</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Dùng Bánh Rice Dango để nâng cấp Namipon Badge.</t>
+          <t>Dùng Bánh Dango Gạo để nâng cấp Huy Hiệu Namipon.</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Tránh chướng ngại vật bằng cách {Cus:Ipt,Touch=tap PC=press Gamepad=press} Nhảy để Bật Nhảy</t>
+          <t>Né chướng ngại vật bằng cách {Cus:Ipt,Touch=tapping PC=pressing Gamepad=pressing} Nhảy để Bật Nhảy</t>
         </is>
       </c>
     </row>
@@ -14159,7 +14159,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Giữ để Xuống Thú nhanh và thực hiện Đòn Xuống Thú.</t>
+          <t>Giữ để Xuống Thú nhanh và thực hiện Tấn Công Xuống Thú.</t>
         </is>
       </c>
     </row>
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem chi tiết Tính Mới Lạ.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết Novelty.</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>{0}{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để xem chi tiết Tính Mới.</t>
+          <t>{0} vào đây để xem chi tiết Vật phẩm Mới.</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem chi tiết Tính Mới Lạ.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết Novelty.</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Vật phẩm Novelty có số lần Uses cố định. Sau khi hết số lần Uses, Novelty sẽ được trả về bộ bài của bạn.</t>
+          <t>Vật phẩm Đặc Biệt có số lần Sử Dụng nhất định. Khi hết số lần dùng, Vật phẩm sẽ được trả về bộ bài của bạn.</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Vật phẩm Novelty có số lần Uses cố định. Sau khi hết số lần Uses, Novelty sẽ được trả về bộ bài của bạn.</t>
+          <t>Vật phẩm Đặc Biệt có số lần Sử Dụng nhất định. Khi hết số lần dùng, Vật phẩm sẽ được trả về bộ bài của bạn.</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Vật phẩm Novelty có số lần Uses cố định. Sau khi hết số lần Uses, Novelty sẽ được trả về bộ bài của bạn.</t>
+          <t>Vật phẩm Đặc Biệt có số lần Sử Dụng nhất định. Khi hết số lần dùng, Vật phẩm sẽ được trả về bộ bài của bạn.</t>
         </is>
       </c>
     </row>
@@ -14614,7 +14614,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Kéo "Novelty" vào ô trống trong Khu Triển Khai để kích hoạt.</t>
+          <t>Kéo Vật Phẩm Mới vào một ô trống trong Khu Triển Khai để kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Kéo "Novelty" vào ô trống trong Khu Triển Khai để kích hoạt.</t>
+          <t>Kéo Vật Phẩm Mới vào một ô trống trong Khu Triển Khai để kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -14744,7 +14744,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Kéo "Novelty" vào ô trống trong Khu Triển Khai để kích hoạt.</t>
+          <t>Kéo Vật Phẩm Mới vào một ô trống trong Khu Triển Khai để kích hoạt.</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Sử dụng Active Skill của Transport Unit XE-01 để Triển khai Nhanh một Echo trên tay.</t>
+          <t>Dùng Kỹ Năng Chủ Động của Đơn Vị Vận Chuyển XE-01 để Triệu Hồi nhanh Echo từ tay cậu</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>{0}Sử dụng Active Skill của Transport Unit XE-01 để Triển khai Nhanh một Echo trên tay.</t>
+          <t>Sử dụng Kỹ Năng Chủ Động của Đơn Vị Vận Chuyển XE-01 để Triệu Hồi nhanh một Echo từ tay bạn.</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Sử dụng Active Skill của Transport Unit XE-01 để Triển khai Nhanh một Echo trên tay.</t>
+          <t>Dùng Kỹ Năng Chủ Động của Đơn Vị Vận Chuyển XE-01 để Triệu Hồi nhanh Echo từ tay cậu</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Giai đoạn Triển khai của vòng hiện tại đã kết thúc. {Cus:Ipt,Touch=Touch PC=Bấm Gamepad=press} vào đây để bắt đầu trận đấu.</t>
+          <t>Giai Đoạn Triển Khai của hiệp hiện tại đã kết thúc. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để bắt đầu trận đấu.</t>
         </is>
       </c>
     </row>
@@ -15069,7 +15069,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Giai đoạn Triển Khai của vòng hiện tại đã kết thúc. Giữ {0} để bắt đầu trận đấu.</t>
+          <t>Giai Đoạn Triển Khai của hiệp hiện tại đã kết thúc. Giữ {0} để bắt đầu trận đấu.</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Giai đoạn Triển Khai của lượt hiện tại đã kết thúc. {Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để bắt đầu trận đấu.</t>
+          <t>Giai Đoạn Triển Khai của hiệp hiện tại đã kết thúc. {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để bắt đầu trận đấu.</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Bạn đã rút Transport Unit XE-01 đã xáo trộn từ bộ bài.</t>
+          <t>Ngươi đã rút được Đơn Vị Vận Chuyển XE-01 đã xáo trộn từ bộ bài của mình</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>{0}Bạn đã rút Transport Unit XE-01 đã xáo trộn từ bộ bài của mình.</t>
+          <t>{0}đã rút được Đơn vị Vận chuyển XE-01 đã xáo trộn từ bộ bài.</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Bạn đã rút Transport Unit XE-01 đã xáo trộn từ bộ bài.</t>
+          <t>Ngươi đã rút được Đơn Vị Vận Chuyển XE-01 đã xáo trộn từ bộ bài của mình</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Hãy thử dùng lại Transport Unit XE-01 để Triển khai Nhanh một Echo có Cost 3.</t>
+          <t>Thử dùng lại Đơn vị Vận Chuyển XE-01 để Triển Khai Nhanh một Echo có Cost 3.</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Hãy thử dùng lại Transport Unit XE-01 để Triển khai Nhanh một Echo có Cost 3.</t>
+          <t>Thử dùng lại Đơn vị Vận Chuyển XE-01 để Triển Khai Nhanh một Echo có Cost 3.</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Hãy thử dùng lại Transport Unit XE-01 để Triển khai Nhanh một Echo có Cost 3.</t>
+          <t>Thử dùng lại Đơn vị Vận Chuyển XE-01 để Triển Khai Nhanh một Echo có Cost 3.</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Kỹ năng Biến Hình của Chest Mimic cho phép bạn rút một Novelty từ bộ bài.</t>
+          <t>Kỹ năng Biến Hình của Quái Thùng Giả cho phép bạn rút một Thẻ Mới Lạ từ bộ bài.</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>{0}Kỹ năng Biến Hình của Rương Giả cho phép bạn rút một Thẻ Mới Lạ từ bộ bài.</t>
+          <t>Kỹ năng Biến Hóa của Chest Mimic cho phép bạn rút một thẻ Novelty từ bộ bài.</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Kỹ năng Biến Hình của Chest Mimic cho phép bạn rút một Novelty từ bộ bài.</t>
+          <t>Kỹ năng Biến Hình của Quái Thùng Giả cho phép bạn rút một Thẻ Mới Lạ từ bộ bài.</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Sử dụng kỹ năng Biến Hình của Chest Mimic để rút lại Transport Unit XE-01 từ bộ bài của bạn.</t>
+          <t>Dùng kỹ năng Biến Hình của Quái Giả Lồng Ngực để rút lại Đơn Vị Vận Chuyển XE-01 từ bộ bài.</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Sử dụng kỹ năng Biến Hình của Chest Mimic để rút lại Transport Unit XE-01 từ bộ bài của bạn.</t>
+          <t>Dùng kỹ năng Biến Hình của Quái Giả Lồng Ngực để rút lại Đơn Vị Vận Chuyển XE-01 từ bộ bài.</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Sử dụng kỹ năng Biến Hình của Chest Mimic để rút lại Transport Unit XE-01 từ bộ bài của bạn.</t>
+          <t>Dùng kỹ năng Biến Hình của Quái Giả Lồng Ngực để rút lại Đơn Vị Vận Chuyển XE-01 từ bộ bài.</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Triển khai Echo có Cost 3 sẽ tăng tiến độ Thử Nghiệm.</t>
+          <t>Triệu hồi Echo có Chi Phí 3 sẽ tăng tiến trình Thử Nghiệm của bạn.</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>{0}Triển khai Echo có Cost 3 sẽ tăng tiến độ Trial của bạn.</t>
+          <t>Triển khai Echo có Cost 3 sẽ tăng tiến độ Thử Nghiệm của bạn.</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Triển khai Echo có Cost 3 sẽ tăng tiến độ Thử Nghiệm.</t>
+          <t>Triệu hồi Echo có Chi Phí 3 sẽ tăng tiến trình Thử Nghiệm của bạn.</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Triển khai Thêm Echoes Mức Cost 3 để hoàn thành Trial.</t>
+          <t>Triển khai thêm Echo có Cost 3 để hoàn thành Thử Thách.</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Triển khai Thêm Echoes Mức Cost 3 để hoàn thành Trial.</t>
+          <t>Triển khai thêm Echo có Cost 3 để hoàn thành Thử Thách.</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Triển khai Thêm Echoes Mức Cost 3 để hoàn thành Trial.</t>
+          <t>Triển khai thêm Echo có Cost 3 để hoàn thành Thử Thách.</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Tái cấu trúc thẻ trong Vùng Triển khai và dùng Transport Unit XE-01 để triển khai Echo mới.</t>
+          <t>Tái cấu trúc một thẻ trong Vùng Triển Khai và sử dụng Đơn vị Vận Chuyển XE-01 để triển khai Echo mới.</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Tái cấu trúc thẻ trong Vùng Triển khai và dùng Transport Unit XE-01 để triển khai Echo mới.</t>
+          <t>Tái cấu trúc một thẻ trong Vùng Triển Khai và sử dụng Đơn vị Vận Chuyển XE-01 để triển khai Echo mới.</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Tái cấu trúc thẻ trong Vùng Triển khai và dùng Transport Unit XE-01 để triển khai Echo mới.</t>
+          <t>Tái cấu trúc một thẻ trong Vùng Triển Khai và sử dụng Đơn vị Vận Chuyển XE-01 để triển khai Echo mới.</t>
         </is>
       </c>
     </row>
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Dùng Transport Unit XE-01 nhiều lần để triển khai Echoes Cost 3 và tăng tốc hoàn thành Trial.</t>
+          <t>Lặp lại sử dụng Đơn Vị Vận Chuyển XE-01 để triển khai Echo có Cost 3 và tăng tốc vượt qua Thử Thách.</t>
         </is>
       </c>
     </row>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Dùng Transport Unit XE-01 nhiều lần để triển khai Echoes Cost 3 và tăng tốc hoàn thành Trial.</t>
+          <t>Lặp lại sử dụng Đơn Vị Vận Chuyển XE-01 để triển khai Echo có Cost 3 và tăng tốc vượt qua Thử Thách.</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Dùng Transport Unit XE-01 nhiều lần để triển khai Echoes Cost 3 và tăng tốc hoàn thành Trial.</t>
+          <t>Lặp lại sử dụng Đơn Vị Vận Chuyển XE-01 để triển khai Echo có Cost 3 và tăng tốc vượt qua Thử Thách.</t>
         </is>
       </c>
     </row>
@@ -16759,7 +16759,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Phép Thử đã hoàn tất. Core Echo trên tay bạn giờ có thể triển khai.</t>
+          <t>Thử thách hoàn tất. Core Echo trên tay cậu giờ có thể triển khai rồi.</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>{0}Thử thách đã hoàn thành. Core Echo trên tay bạn giờ có thể triển khai.</t>
+          <t>Thử Nghiệm hoàn tất. Echo Cốt Lõi trên tay bạn giờ có thể triển khai.</t>
         </is>
       </c>
     </row>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Phép Thử đã hoàn tất. Core Echo trên tay bạn giờ có thể triển khai.</t>
+          <t>Thử thách hoàn tất. Core Echo trên tay cậu giờ có thể triển khai rồi.</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Triển khai Core Echo không tiêu hao Energy.</t>
+          <t>Triển khai Tâm Ảnh Cốt không tiêu hao Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Triển khai Core Echo không tiêu hao Energy.</t>
+          <t>Triển khai Tâm Ảnh Cốt không tiêu hao Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Triển khai Core Echo không tiêu hao Energy.</t>
+          <t>Triển khai Tâm Ảnh Cốt không tiêu hao Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -17150,8 +17150,8 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Triển khai Core Echoes.
-Core Echoes không thể Modulate hoặc Reconstruct.</t>
+          <t>Triển khai Core Echo.
+Core Echo không thể bị Điều Chỉnh hay Tái Cấu Trúc.</t>
         </is>
       </c>
     </row>
@@ -17217,8 +17217,8 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Triển khai Core Echoes.
-Core Echoes không thể Modulate hoặc Reconstruct.</t>
+          <t>Triển khai Core Echo.
+Core Echo không thể bị Điều Chỉnh hay Tái Cấu Trúc.</t>
         </is>
       </c>
     </row>
@@ -17284,8 +17284,8 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Triển khai Core Echoes.
-Core Echoes không thể Modulate hoặc Reconstruct.</t>
+          <t>Triển khai Core Echo.
+Core Echo không thể bị Điều Chỉnh hay Tái Cấu Trúc.</t>
         </is>
       </c>
     </row>
@@ -17350,7 +17350,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Bạn chỉ có thể triển khai tối đa 4 Echoes trong Khu Triển khai.</t>
+          <t>Cậu chỉ có thể triển khai tối đa 4 Echo trên Vùng Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -17415,7 +17415,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Bạn chỉ có thể triển khai tối đa 4 Echoes trong Khu Triển khai.</t>
+          <t>Cậu chỉ có thể triển khai tối đa 4 Echo trên Vùng Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -17480,7 +17480,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Bạn chỉ có thể triển khai tối đa 4 Echoes trong Khu Triển khai.</t>
+          <t>Cậu chỉ có thể triển khai tối đa 4 Echo trên Vùng Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Novelty không giới hạn số lần triển khai. Bạn có thể tiếp tục triển khai Novelty trên tay.</t>
+          <t>Vật phẩm Đặc Biệt không giới hạn triển khai. Bạn có thể tiếp tục đặt Vật phẩm trong tay xuống bàn.</t>
         </is>
       </c>
     </row>
@@ -17610,7 +17610,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Novelty không giới hạn số lần triển khai. Bạn có thể tiếp tục triển khai Novelty trên tay.</t>
+          <t>Vật phẩm Đặc Biệt không giới hạn triển khai. Bạn có thể tiếp tục đặt Vật phẩm trong tay xuống bàn.</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Novelty không giới hạn số lần triển khai. Bạn có thể tiếp tục triển khai Novelty trên tay.</t>
+          <t>Vật phẩm Đặc Biệt không giới hạn triển khai. Bạn có thể tiếp tục đặt Vật phẩm trong tay xuống bàn.</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Sử dụng Hornett sẽ kết thúc Giai đoạn Triển khai.</t>
+          <t>Sử dụng Hornett sẽ kết thúc Giai Đoạn Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Sử dụng Hornett sẽ kết thúc Giai đoạn Triển khai.</t>
+          <t>Sử dụng Hornett sẽ kết thúc Giai Đoạn Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -17870,7 +17870,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Sử dụng Hornett sẽ kết thúc Giai đoạn Triển khai.</t>
+          <t>Sử dụng Hornett sẽ kết thúc Giai Đoạn Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Đối thủ đã sử dụng Domain. Bạn có thể xem kỹ năng Domain của họ tại đây.</t>
+          <t>Đối thủ đã sử dụng Lãnh Địa. Cậu có thể xem kỹ năng Lãnh Địa của họ tại đây.</t>
         </is>
       </c>
     </row>
@@ -18000,7 +18000,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Đối thủ đã sử dụng Domain. Bạn có thể xem kỹ năng Domain của họ tại đây.</t>
+          <t>Đối thủ đã sử dụng Lãnh Địa. Cậu có thể xem kỹ năng Lãnh Địa của họ tại đây.</t>
         </is>
       </c>
     </row>
@@ -18065,7 +18065,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Đối thủ đã sử dụng Domain. Bạn có thể xem kỹ năng Domain của họ tại đây.</t>
+          <t>Đối thủ đã sử dụng Lãnh Địa. Cậu có thể xem kỹ năng Lãnh Địa của họ tại đây.</t>
         </is>
       </c>
     </row>
@@ -18130,7 +18130,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Kỹ năng Domain của đối thủ ngăn bạn nhận Energy thông qua Reconstruction.</t>
+          <t>Kỹ năng Lãnh Địa của đối thủ ngăn cậu hồi năng lượng qua Tái Cấu Trúc.</t>
         </is>
       </c>
     </row>
@@ -18195,7 +18195,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Kỹ năng Domain của đối thủ ngăn bạn nhận Energy thông qua Reconstruction.</t>
+          <t>Kỹ năng Lãnh Địa của đối thủ ngăn cậu hồi năng lượng qua Tái Cấu Trúc.</t>
         </is>
       </c>
     </row>
@@ -18260,7 +18260,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Kỹ năng Domain của đối thủ ngăn bạn nhận Energy thông qua Reconstruction.</t>
+          <t>Kỹ năng Lãnh Địa của đối thủ ngăn cậu hồi năng lượng qua Tái Cấu Trúc.</t>
         </is>
       </c>
     </row>
@@ -18325,7 +18325,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào thẻ để xem kỹ năng Domain của bạn.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào thẻ bài để xem kỹ năng Domain của bạn.</t>
         </is>
       </c>
     </row>
@@ -18390,7 +18390,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>{0}{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào thẻ để xem kỹ năng Domain của bạn.</t>
+          <t>{0} vào thẻ bài để xem kỹ năng Lãnh Địa của cậu.</t>
         </is>
       </c>
     </row>
@@ -18455,7 +18455,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào thẻ để xem kỹ năng Domain của bạn.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào thẻ bài để xem kỹ năng Domain của bạn.</t>
         </is>
       </c>
     </row>
@@ -18520,7 +18520,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Lãnh Địa của bạn có Active Skill có thể triển khai Echoes.</t>
+          <t>Lãnh Địa của ngươi có Kỹ Năng Chủ Động để triển khai Tâm Âm.</t>
         </is>
       </c>
     </row>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Lãnh Địa của bạn có Active Skill có thể triển khai Echoes.</t>
+          <t>Lãnh Địa của ngươi có Kỹ Năng Chủ Động để triển khai Tâm Âm.</t>
         </is>
       </c>
     </row>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Lãnh Địa của bạn có Active Skill có thể triển khai Echoes.</t>
+          <t>Lãnh Địa của ngươi có Kỹ Năng Chủ Động để triển khai Tâm Âm.</t>
         </is>
       </c>
     </row>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Place thẻ Domain vào khu vực Biến Đổi để sử dụng kỹ năng của nó.</t>
+          <t>Đặt thẻ Khu Vực vào Khu Vực Biến Đổi để sử dụng kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -18780,7 +18780,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Place thẻ Domain vào khu vực Biến Đổi để sử dụng kỹ năng của nó.</t>
+          <t>Đặt thẻ Khu Vực vào Khu Vực Biến Đổi để sử dụng kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Place thẻ Domain vào khu vực Biến Đổi để sử dụng kỹ năng của nó.</t>
+          <t>Đặt thẻ Khu Vực vào Khu Vực Biến Đổi để sử dụng kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Lãnh Địa của bạn có thể Triệu Hồi Nhanh một Echo mỗi lượt mà không cần dùng Năng Lượng.</t>
+          <t>Lãnh Địa của ngươi có thể Triển Khai Nhanh một Tâm Âm mỗi lượt mà không tốn Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -18975,7 +18975,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Lãnh Địa của bạn có thể Triệu Hồi Nhanh một Echo mỗi lượt mà không cần dùng Năng Lượng.</t>
+          <t>Lãnh Địa của ngươi có thể Triển Khai Nhanh một Tâm Âm mỗi lượt mà không tốn Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -19040,7 +19040,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Lãnh Địa của bạn có thể Triệu Hồi Nhanh một Echo mỗi lượt mà không cần dùng Năng Lượng.</t>
+          <t>Lãnh Địa của ngươi có thể Triển Khai Nhanh một Tâm Âm mỗi lượt mà không tốn Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -19105,7 +19105,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Chọn Stonewall Bracer để Triển khai Nhanh.</t>
+          <t>Chọn Vòng Tay Stonewall để Triển Khai Nhanh</t>
         </is>
       </c>
     </row>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Chọn Stonewall Bracer để Triển khai Nhanh.</t>
+          <t>Chọn Vòng Tay Stonewall để Triển Khai Nhanh</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Chọn Stonewall Bracer để Triển khai Nhanh.</t>
+          <t>Chọn Vòng Tay Stonewall để Triển Khai Nhanh</t>
         </is>
       </c>
     </row>
@@ -19300,7 +19300,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Sử dụng kỹ năng Biến Hình của Dwarf Cassowary và kết thúc Giai Đoạn Triển Khai</t>
+          <t>Dùng kỹ năng Biến Hình của Dwarf Cassowary và kết thúc Giai Đoạn Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -19365,7 +19365,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Sử dụng kỹ năng Biến Hình của Dwarf Cassowary và kết thúc Giai Đoạn Triển Khai</t>
+          <t>Dùng kỹ năng Biến Hình của Dwarf Cassowary và kết thúc Giai Đoạn Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Sử dụng kỹ năng Biến Hình của Dwarf Cassowary và kết thúc Giai Đoạn Triển Khai</t>
+          <t>Dùng kỹ năng Biến Hình của Dwarf Cassowary và kết thúc Giai Đoạn Triển Khai.</t>
         </is>
       </c>
     </row>
@@ -19495,7 +19495,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Active Skill của Domain sẽ được đặt lại khi bắt đầu mỗi vòng.</t>
+          <t>Kỹ năng Chủ động của Tổ Tacet sẽ được đặt lại vào đầu mỗi lượt.</t>
         </is>
       </c>
     </row>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Active Skill của Domain sẽ được đặt lại khi bắt đầu mỗi vòng.</t>
+          <t>Kỹ năng Chủ động của Tổ Tacet sẽ được đặt lại vào đầu mỗi lượt.</t>
         </is>
       </c>
     </row>
@@ -19625,7 +19625,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Active Skill của Domain sẽ được đặt lại khi bắt đầu mỗi vòng.</t>
+          <t>Kỹ năng Chủ động của Tổ Tacet sẽ được đặt lại vào đầu mỗi lượt.</t>
         </is>
       </c>
     </row>
@@ -19690,7 +19690,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Triển khai Spacetrek Explorer, kỹ năng của nó cho phép bạn rút một Mining Reindeer từ bộ bài.</t>
+          <t>Triển khai Spacetrek Explorer, kỹ năng của nó cho phép cậu rút một Mining Reindeer từ bộ bài.</t>
         </is>
       </c>
     </row>
@@ -19755,7 +19755,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Triển khai Spacetrek Explorer, kỹ năng của nó cho phép bạn rút một Mining Reindeer từ bộ bài.</t>
+          <t>Triển khai Spacetrek Explorer, kỹ năng của nó cho phép cậu rút một Mining Reindeer từ bộ bài.</t>
         </is>
       </c>
     </row>
@@ -19820,7 +19820,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Triển khai Spacetrek Explorer, kỹ năng của nó cho phép bạn rút một Mining Reindeer từ bộ bài.</t>
+          <t>Triển khai Spacetrek Explorer, kỹ năng của nó cho phép cậu rút một Mining Reindeer từ bộ bài.</t>
         </is>
       </c>
     </row>
@@ -19885,7 +19885,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hiện không thể nhận Energy qua Reconstruction. Không thể dùng thẻ này.</t>
+          <t>Hiện tại không thể nhận Năng Lượng qua Tái Cấu Trúc. Không thể sử dụng thẻ này.</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Hiện không thể nhận Energy qua Reconstruction. Không thể dùng thẻ này.</t>
+          <t>Hiện tại không thể nhận Năng Lượng qua Tái Cấu Trúc. Không thể sử dụng thẻ này.</t>
         </is>
       </c>
     </row>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Hiện không thể nhận Energy qua Reconstruction. Không thể dùng thẻ này.</t>
+          <t>Hiện tại không thể nhận Năng Lượng qua Tái Cấu Trúc. Không thể sử dụng thẻ này.</t>
         </is>
       </c>
     </row>
@@ -20080,7 +20080,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Ngoài Active Skill, Khu Vực này còn có hiệu ứng Nạp Năng.</t>
+          <t>Ngoài Kỹ năng Chủ động, Tổ Tacet này còn có hiệu ứng Nạp năng lượng.</t>
         </is>
       </c>
     </row>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Ngoài Active Skill, Khu Vực này còn có hiệu ứng Nạp Năng.</t>
+          <t>Ngoài Kỹ năng Chủ động, Tổ Tacet này còn có hiệu ứng Nạp năng lượng.</t>
         </is>
       </c>
     </row>
@@ -20210,7 +20210,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Ngoài Active Skill, Khu Vực này còn có hiệu ứng Nạp Năng.</t>
+          <t>Ngoài Kỹ năng Chủ động, Tổ Tacet này còn có hiệu ứng Nạp năng lượng.</t>
         </is>
       </c>
     </row>
@@ -20276,7 +20276,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Active Skill của Lãnh Địa sẽ được đặt lại sau khi Tái Cấu trúc 4 lá bài.
+          <t>Kỹ năng Chủ động của Tổ Tacet sẽ được đặt lại sau khi Tái Cấu trúc 4 lá bài.
 Chọn 4 lá bài từ tay bạn để Tái Cấu trúc.</t>
         </is>
       </c>
@@ -20343,7 +20343,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Active Skill của Lãnh Địa sẽ được đặt lại sau khi Tái Cấu trúc 4 lá bài.
+          <t>Kỹ năng Chủ động của Tổ Tacet sẽ được đặt lại sau khi Tái Cấu trúc 4 lá bài.
 Chọn 4 lá bài từ tay bạn để Tái Cấu trúc.</t>
         </is>
       </c>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Active Skill của Lãnh Địa sẽ được đặt lại sau khi Tái Cấu trúc 4 lá bài.
+          <t>Kỹ năng Chủ động của Tổ Tacet sẽ được đặt lại sau khi Tái Cấu trúc 4 lá bài.
 Chọn 4 lá bài từ tay bạn để Tái Cấu trúc.</t>
         </is>
       </c>
@@ -20477,8 +20477,8 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Bạn có thể sử dụng Active Skill của Domain trong lượt này.
-Dùng Active Skill để Triển khai Nhanh một Echo.</t>
+          <t>Lượt này cậu có thể dùng lại Kỹ Năng Chủ Động của Lãnh Địa.
+Dùng Kỹ Năng Chủ Động để Triệu Hồi Nhanh một Echo.</t>
         </is>
       </c>
     </row>
@@ -20544,8 +20544,8 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Bạn có thể sử dụng Active Skill của Domain trong lượt này.
-Dùng Active Skill để Triển khai Nhanh một Echo.</t>
+          <t>Lượt này cậu có thể dùng lại Kỹ Năng Chủ Động của Lãnh Địa.
+Dùng Kỹ Năng Chủ Động để Triệu Hồi Nhanh một Echo.</t>
         </is>
       </c>
     </row>
@@ -20611,8 +20611,8 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Bạn có thể sử dụng Active Skill của Domain trong lượt này.
-Dùng Active Skill để Triển khai Nhanh một Echo.</t>
+          <t>Lượt này cậu có thể dùng lại Kỹ Năng Chủ Động của Lãnh Địa.
+Dùng Kỹ Năng Chủ Động để Triệu Hồi Nhanh một Echo.</t>
         </is>
       </c>
     </row>
@@ -20677,7 +20677,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Hãy tận dụng chiến thuật hiện có và đánh bại đối thủ.</t>
+          <t>Giờ thì dùng hết chiến thuật mình có mà đánh bại đối thủ đi.</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Hãy tận dụng chiến thuật hiện có và đánh bại đối thủ.</t>
+          <t>Giờ thì dùng hết chiến thuật mình có mà đánh bại đối thủ đi.</t>
         </is>
       </c>
     </row>
@@ -20807,7 +20807,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Hãy tận dụng chiến thuật hiện có và đánh bại đối thủ.</t>
+          <t>Giờ thì dùng hết chiến thuật mình có mà đánh bại đối thủ đi.</t>
         </is>
       </c>
     </row>
@@ -20872,7 +20872,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Xem mẹo và chiến thuật trong bách khoa thư Peaks of Prestige tại đây.</t>
+          <t>Xem mẹo và chiến thuật trong bộ bách khoa Peaks of Prestige tại đây.</t>
         </is>
       </c>
     </row>
@@ -20937,7 +20937,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>{0}Xem mẹo và chiến thuật trong bách khoa Peaks of Prestige tại đây.</t>
+          <t>Xem mẹo và chiến thuật trong bách khoa toàn thư Peaks of Prestige tại đây.</t>
         </is>
       </c>
     </row>
@@ -21002,7 +21002,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Xem mẹo và chiến thuật trong bách khoa thư Peaks of Prestige tại đây.</t>
+          <t>Xem mẹo và chiến thuật trong bộ bách khoa Peaks of Prestige tại đây.</t>
         </is>
       </c>
     </row>
@@ -21067,7 +21067,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Sau khi Biến Đổi hoàn tất, thẻ đã chọn sẽ được đưa vào tay bạn.</t>
+          <t>Sau khi Biến Hình hoàn tất, lá bài đã chọn sẽ được đưa vào tay cậu.</t>
         </is>
       </c>
     </row>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>{0}Sau khi Biến Hóa hoàn tất, thẻ đã chọn sẽ được đưa vào tay bạn.</t>
+          <t>Sau khi hoàn tất Biến Hóa, thẻ đã chọn sẽ được đưa vào tay bạn.</t>
         </is>
       </c>
     </row>
@@ -21197,7 +21197,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Sau khi Biến Đổi hoàn tất, thẻ đã chọn sẽ được đưa vào tay bạn.</t>
+          <t>Sau khi Biến Hình hoàn tất, lá bài đã chọn sẽ được đưa vào tay cậu.</t>
         </is>
       </c>
     </row>
@@ -21262,7 +21262,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Bạn có thể xem tính năng của xe máy thám hiểm trong Terminal</t>
+          <t>Bạn có thể xem các tính năng của xe máy thám hiểm tại Thiết bị đầu cuối</t>
         </is>
       </c>
     </row>
@@ -21327,7 +21327,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>{0}Bạn có thể xem các tính năng của xe máy thám hiểm trong Terminal</t>
+          <t>{0}có thể xem tính năng của xe máy thám hiểm tại Thiết bị đầu cuối.</t>
         </is>
       </c>
     </row>
@@ -21392,7 +21392,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Bạn có thể xem tính năng của xe máy thám hiểm trong Terminal</t>
+          <t>Bạn có thể xem các tính năng của xe máy thám hiểm tại Thiết bị đầu cuối</t>
         </is>
       </c>
     </row>
@@ -21457,7 +21457,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Xem nâng cấp xe máy thám hiểm và Mô-đun Mở Rộng.</t>
+          <t>Xem nâng cấp mô-tô thám hiểm và Mô-đun Mở Rộng</t>
         </is>
       </c>
     </row>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Xem nâng cấp xe máy thám hiểm và Mô-đun Mở Rộng.</t>
+          <t>Xem nâng cấp mô-tô thám hiểm và Mô-đun Mở Rộng</t>
         </is>
       </c>
     </row>
@@ -21587,7 +21587,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Xem nâng cấp xe máy thám hiểm và Mô-đun Mở Rộng.</t>
+          <t>Xem nâng cấp mô-tô thám hiểm và Mô-đun Mở Rộng</t>
         </is>
       </c>
     </row>
@@ -21652,7 +21652,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Cấp Độ Cải Tiến Xe Máy tăng khi bạn khám phá thế giới.</t>
+          <t>Cấp Độ Nâng Cấp Xe Máy tăng khi bạn khám phá thế giới.</t>
         </is>
       </c>
     </row>
@@ -21717,7 +21717,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Cấp Độ Cải Tiến Xe Máy tăng khi bạn khám phá thế giới.</t>
+          <t>Cấp Độ Nâng Cấp Xe Máy tăng khi bạn khám phá thế giới.</t>
         </is>
       </c>
     </row>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Cấp Độ Cải Tiến Xe Máy tăng khi bạn khám phá thế giới.</t>
+          <t>Cấp Độ Nâng Cấp Xe Máy tăng khi bạn khám phá thế giới.</t>
         </is>
       </c>
     </row>
@@ -21847,7 +21847,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Increase Cấp Độ Mod để cải thiện hiệu suất xe máy thám hiểm của bạn.</t>
+          <t>Nâng cấp Cấp độ Mod để cải thiện hiệu suất xe máy thám hiểm của bạn.</t>
         </is>
       </c>
     </row>
@@ -21912,7 +21912,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Increase Cấp Độ Mod để cải thiện hiệu suất xe máy thám hiểm của bạn.</t>
+          <t>Nâng cấp Cấp độ Mod để cải thiện hiệu suất xe máy thám hiểm của bạn.</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Increase Cấp Độ Mod để cải thiện hiệu suất xe máy thám hiểm của bạn.</t>
+          <t>Nâng cấp Cấp độ Mod để cải thiện hiệu suất xe máy thám hiểm của bạn.</t>
         </is>
       </c>
     </row>
@@ -22042,7 +22042,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem Mô-đun Mở Rộng Xe Thám Hiểm</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem các Mô-đun Mở Rộng cho xe máy thám hiểm.</t>
         </is>
       </c>
     </row>
@@ -22107,7 +22107,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem Mô-đun Mở Rộng Xe Thám Hiểm</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem các Mô-đun Mở Rộng cho xe máy thám hiểm.</t>
         </is>
       </c>
     </row>
@@ -22172,7 +22172,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem Mô-đun Mở Rộng Xe Thám Hiểm</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem các Mô-đun Mở Rộng cho xe máy thám hiểm.</t>
         </is>
       </c>
     </row>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Mô-đun Mở Rộng cung cấp cho xe máy thám hiểm những nâng cấp hiệu suất độc đáo</t>
+          <t>Mô-đun Mở Rộng nâng cấp hiệu suất độc đáo cho xe máy thám hiểm</t>
         </is>
       </c>
     </row>
@@ -22302,7 +22302,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Mô-đun Mở Rộng cung cấp cho xe máy thám hiểm những nâng cấp hiệu suất độc đáo</t>
+          <t>Mô-đun Mở Rộng nâng cấp hiệu suất độc đáo cho xe máy thám hiểm</t>
         </is>
       </c>
     </row>
@@ -22367,7 +22367,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Mô-đun Mở Rộng cung cấp cho xe máy thám hiểm những nâng cấp hiệu suất độc đáo</t>
+          <t>Mô-đun Mở Rộng nâng cấp hiệu suất độc đáo cho xe máy thám hiểm</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem Nhiệm Vụ Mod và kiếm Points Mod</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Nhiệm Vụ Modding và kiếm Điểm Modding.</t>
         </is>
       </c>
     </row>
@@ -22497,7 +22497,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem Nhiệm Vụ Mod và kiếm Points Mod</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Nhiệm Vụ Modding và kiếm Điểm Modding.</t>
         </is>
       </c>
     </row>
@@ -22562,7 +22562,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để xem Nhiệm Vụ Mod và kiếm Points Mod</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Nhiệm Vụ Modding và kiếm Điểm Modding.</t>
         </is>
       </c>
     </row>
@@ -22627,7 +22627,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Xem các cách kiếm Điểm Kinh Nghiệm Modding tại đây.</t>
+          <t>Xem cách kiếm Điểm Modding EXP tại đây.</t>
         </is>
       </c>
     </row>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Xem các cách kiếm Điểm Kinh Nghiệm Modding tại đây.</t>
+          <t>Xem cách kiếm Điểm Modding EXP tại đây.</t>
         </is>
       </c>
     </row>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Xem các cách kiếm Điểm Kinh Nghiệm Modding tại đây.</t>
+          <t>Xem cách kiếm Điểm Modding EXP tại đây.</t>
         </is>
       </c>
     </row>
@@ -22822,7 +22822,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Tùy chỉnh Livery cho xe máy thám hiểm của bạn tại đây.</t>
+          <t>Tùy chỉnh lớp sơn xe máy thám hiểm của bạn tại đây.</t>
         </is>
       </c>
     </row>
@@ -22887,7 +22887,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Tùy chỉnh Livery cho xe máy thám hiểm của bạn tại đây.</t>
+          <t>Tùy chỉnh lớp sơn xe máy thám hiểm của bạn tại đây.</t>
         </is>
       </c>
     </row>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Tùy chỉnh Livery cho xe máy thám hiểm của bạn tại đây.</t>
+          <t>Tùy chỉnh lớp sơn xe máy thám hiểm của bạn tại đây.</t>
         </is>
       </c>
     </row>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Dùng {0} để lên xe máy ngay lập tức</t>
+          <t>Dùng {0} để lên xe máy ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -23082,7 +23082,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Dùng {0} để lên xe máy ngay lập tức</t>
+          <t>Dùng {0} để lên xe máy ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -23147,7 +23147,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Dùng Công cụ: Lên Xe Nhanh để lên xe máy ngay lập tức</t>
+          <t>Dùng Tiện Ích: Lên Xe Nhanh để lên xe máy ngay lập tức.</t>
         </is>
       </c>
     </row>
@@ -23212,7 +23212,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Bạn có thể vào Cinematic Mode khi Tự Động Điều Khiển đang kích hoạt</t>
+          <t>Cậu có thể vào Chế Độ Điện Ảnh khi Chế Độ Tự Lái đang kích hoạt</t>
         </is>
       </c>
     </row>
@@ -23277,7 +23277,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Bạn có thể vào Cinematic Mode khi Tự Động Điều Khiển đang kích hoạt</t>
+          <t>Cậu có thể vào Chế Độ Điện Ảnh khi Chế Độ Tự Lái đang kích hoạt</t>
         </is>
       </c>
     </row>
@@ -23342,7 +23342,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Chế độ Điện ảnh cho phép mời Resonators tham gia Đi Chung</t>
+          <t>Chế Độ Điện Ảnh cho phép cậu mời Resonator tham gia Hành Trình Chung</t>
         </is>
       </c>
     </row>
@@ -23407,7 +23407,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Pause hoặc chuyển bài nhạc tại đây</t>
+          <t>Tạm dừng hoặc đổi bản nhạc tại đây</t>
         </is>
       </c>
     </row>
@@ -23472,7 +23472,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Pause hoặc chuyển bài nhạc tại đây</t>
+          <t>Tạm dừng hoặc đổi bản nhạc tại đây</t>
         </is>
       </c>
     </row>
@@ -23537,7 +23537,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Pause hoặc chuyển bài nhạc tại đây</t>
+          <t>Tạm dừng hoặc đổi bản nhạc tại đây</t>
         </is>
       </c>
     </row>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Chọn một vị trí trên bản đồ để thiết lập lộ trình di chuyển.</t>
+          <t>Chọn vị trí trên bản đồ để thiết lập lộ trình di chuyển.</t>
         </is>
       </c>
     </row>
@@ -23667,7 +23667,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Chọn một vị trí trên bản đồ để thiết lập lộ trình di chuyển.</t>
+          <t>Chọn vị trí trên bản đồ để thiết lập lộ trình di chuyển.</t>
         </is>
       </c>
     </row>
@@ -23732,7 +23732,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Chọn một vị trí trên bản đồ để thiết lập lộ trình di chuyển.</t>
+          <t>Chọn vị trí trên bản đồ để thiết lập lộ trình di chuyển.</t>
         </is>
       </c>
     </row>
@@ -23798,8 +23798,8 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Spearback có Energy Cost là 3.
-Hiện bạn không đủ Energy. Hãy biến hình Sabyr Boar để nhận 2 điểm Energy.</t>
+          <t>Spearback có Chi Phí Năng Lượng là 3.
+Hiện tại cậu không đủ Năng Lượng. Hãy Biến Hình Sabyr Boar để nhận 2 điểm Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -23865,8 +23865,8 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Spearback có Energy Cost là 3.
-Hiện bạn không đủ Energy. Hãy biến hình Sabyr Boar để nhận 2 điểm Energy.</t>
+          <t>Spearback có Chi Phí Năng Lượng là 3.
+Hiện tại cậu không đủ Năng Lượng. Hãy Biến Hình Sabyr Boar để nhận 2 điểm Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -23932,8 +23932,8 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Spearback có Energy Cost là 3.
-Hiện bạn không đủ Energy. Hãy biến hình Sabyr Boar để nhận 2 điểm Energy.</t>
+          <t>Spearback có Chi Phí Năng Lượng là 3.
+Hiện tại cậu không đủ Năng Lượng. Hãy Biến Hình Sabyr Boar để nhận 2 điểm Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -23998,7 +23998,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Triệu hồi một La Guardia từ tay bài và kết thúc lượt.</t>
+          <t>Triển khai một La Guardia từ tay cậu và kết thúc lượt đi.</t>
         </is>
       </c>
     </row>
@@ -24063,7 +24063,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Triệu hồi một La Guardia từ tay bài và kết thúc lượt.</t>
+          <t>Triển khai một La Guardia từ tay cậu và kết thúc lượt đi.</t>
         </is>
       </c>
     </row>
@@ -24128,7 +24128,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Triệu hồi một La Guardia từ tay bài và kết thúc lượt.</t>
+          <t>Triển khai một La Guardia từ tay cậu và kết thúc lượt đi.</t>
         </is>
       </c>
     </row>
@@ -24194,8 +24194,8 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Echoes của bạn đã được tăng cường.
-Sau khi vòng đấu kết thúc, các lá bài không dùng sẽ được xáo lại vào bộ bài.</t>
+          <t>Echo của cậu đã được tăng cường.
+Sau khi lượt kết thúc, các lá bài chưa dùng sẽ được xáo lại vào bộ bài.</t>
         </is>
       </c>
     </row>
@@ -24261,8 +24261,8 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>{0}Echoes của bạn đã được tăng cường.
-Sau khi lượt kết thúc, các lá bài chưa dùng sẽ được xáo lại vào bộ bài.</t>
+          <t>Âm vang của {0}đã được tăng cường.
+Sau khi vòng đấu kết thúc, các thẻ chưa dùng sẽ được xáo lại vào bộ bài.</t>
         </is>
       </c>
     </row>
@@ -24328,8 +24328,8 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Echoes của bạn đã được tăng cường.
-Sau khi vòng đấu kết thúc, các lá bài không dùng sẽ được xáo lại vào bộ bài.</t>
+          <t>Echo của cậu đã được tăng cường.
+Sau khi lượt kết thúc, các lá bài chưa dùng sẽ được xáo lại vào bộ bài.</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Kỹ năng Biến Hình của Dwarf Cassowary có thể tăng sức mạnh cho Echoes của bạn.</t>
+          <t>Kỹ năng Biến Hình của Dwarf Cassowary có thể tăng sức mạnh cho Echo của cậu.</t>
         </is>
       </c>
     </row>
@@ -24459,7 +24459,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Kỹ năng Biến Hình của Dwarf Cassowary có thể tăng sức mạnh cho Echoes của bạn.</t>
+          <t>Kỹ năng Biến Hình của Dwarf Cassowary có thể tăng sức mạnh cho Echo của cậu.</t>
         </is>
       </c>
     </row>
@@ -24524,7 +24524,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Kỹ năng Biến Hình của Dwarf Cassowary có thể tăng sức mạnh cho Echoes của bạn.</t>
+          <t>Kỹ năng Biến Hình của Dwarf Cassowary có thể tăng sức mạnh cho Echo của cậu.</t>
         </is>
       </c>
     </row>
@@ -24589,7 +24589,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Bạn cũng có thể tiêu hao Energy để sử dụng Resonator Tactics và tăng cường Echoes.</t>
+          <t>Cậu cũng có thể tiêu hao Năng Lượng để sử dụng Chiến Thuật Cộng Hưởng và tăng cường Echo của mình.</t>
         </is>
       </c>
     </row>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Bạn cũng có thể tiêu hao Energy để sử dụng Resonator Tactics và tăng cường Echoes.</t>
+          <t>Cậu cũng có thể tiêu hao Năng Lượng để sử dụng Chiến Thuật Cộng Hưởng và tăng cường Echo của mình.</t>
         </is>
       </c>
     </row>
@@ -24719,7 +24719,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Bạn cũng có thể tiêu hao Energy để sử dụng Resonator Tactics và tăng cường Echoes.</t>
+          <t>Cậu cũng có thể tiêu hao Năng Lượng để sử dụng Chiến Thuật Cộng Hưởng và tăng cường Echo của mình.</t>
         </is>
       </c>
     </row>
@@ -24785,8 +24785,8 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Echoes trong Khu Vực Triển Khai cũng có thể Reconstruct.
-Reconstruct La Guardia để nhận Energy.</t>
+          <t>Echo trong Deployment Zone cũng có thể được Tái cấu trúc.
+Tái cấu trúc La Guardia để nhận Năng lượng.</t>
         </is>
       </c>
     </row>
@@ -24852,8 +24852,8 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Echoes trong Khu Vực Triển Khai cũng có thể Reconstruct.
-Reconstruct La Guardia để nhận Energy.</t>
+          <t>Echo trong Deployment Zone cũng có thể được Tái cấu trúc.
+Tái cấu trúc La Guardia để nhận Năng lượng.</t>
         </is>
       </c>
     </row>
@@ -24919,8 +24919,8 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Echoes trong Khu Vực Triển Khai cũng có thể Reconstruct.
-Reconstruct La Guardia để nhận Energy.</t>
+          <t>Echo trong Deployment Zone cũng có thể được Tái cấu trúc.
+Tái cấu trúc La Guardia để nhận Năng lượng.</t>
         </is>
       </c>
     </row>
@@ -24985,7 +24985,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Chest Mimic có thể phát hiện Novelties trong bộ bài của bạn. Hãy thử dùng kỹ năng Biến Hình của nó.</t>
+          <t>Rương Biến Hình có thể phát hiện Đồ Vật Lạ trong bộ bài của cậu. Hãy thử dùng kỹ năng Biến Hình của nó.</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Chest Mimic có thể phát hiện Novelties trong bộ bài của bạn. Hãy thử dùng kỹ năng Biến Hình của nó.</t>
+          <t>Rương Biến Hình có thể phát hiện Đồ Vật Lạ trong bộ bài của cậu. Hãy thử dùng kỹ năng Biến Hình của nó.</t>
         </is>
       </c>
     </row>
@@ -25115,7 +25115,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Chest Mimic có thể phát hiện Novelties trong bộ bài của bạn. Hãy thử dùng kỹ năng Biến Hình của nó.</t>
+          <t>Rương Biến Hình có thể phát hiện Đồ Vật Lạ trong bộ bài của cậu. Hãy thử dùng kỹ năng Biến Hình của nó.</t>
         </is>
       </c>
     </row>
@@ -25180,7 +25180,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Novelty này có Active Skill, chỉ có thể dùng một lần mỗi lượt.</t>
+          <t>Kỹ năng Chủ Động của Món Đồ Mới này chỉ có thể sử dụng một lần mỗi lượt.</t>
         </is>
       </c>
     </row>
@@ -25245,7 +25245,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>{0}Novelty này có Active Skill, chỉ có thể sử dụng một lần mỗi lượt.</t>
+          <t>Thẻ Novelty này có Kỹ Năng Chủ Động, chỉ có thể sử dụng một lần mỗi lượt.</t>
         </is>
       </c>
     </row>
@@ -25310,7 +25310,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Novelty này có Active Skill, chỉ có thể dùng một lần mỗi lượt.</t>
+          <t>Kỹ năng Chủ Động của Món Đồ Mới này chỉ có thể sử dụng một lần mỗi lượt.</t>
         </is>
       </c>
     </row>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Chọn Stonewall Bracer để Triển khai nhanh. Không tốn Energy.</t>
+          <t>Chọn Vòng Tay Stonewall để Triển Khai Nhanh. Không tốn Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -25440,7 +25440,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Chọn Stonewall Bracer để Triển khai nhanh. Không tốn Energy.</t>
+          <t>Chọn Vòng Tay Stonewall để Triển Khai Nhanh. Không tốn Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -25505,7 +25505,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Chọn Stonewall Bracer để Triển khai nhanh. Không tốn Energy.</t>
+          <t>Chọn Vòng Tay Stonewall để Triển Khai Nhanh. Không tốn Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -25570,7 +25570,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xác nhận triển khai.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xác nhận triển khai.</t>
         </is>
       </c>
     </row>
@@ -25635,7 +25635,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xác nhận triển khai.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xác nhận triển khai.</t>
         </is>
       </c>
     </row>
@@ -25700,7 +25700,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xác nhận triển khai.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xác nhận triển khai.</t>
         </is>
       </c>
     </row>
@@ -25765,7 +25765,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Một số đòn tấn công tích lũy Off-Tune Level cho một số kẻ địch nhất định</t>
+          <t>Một số đòn tấn công tích lũy Mức Lệch Nhịp cho một số kẻ địch nhất định.</t>
         </is>
       </c>
     </row>
@@ -25830,7 +25830,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Một số đòn tấn công tích lũy Off-Tune Level cho một số kẻ địch nhất định</t>
+          <t>Một số đòn tấn công tích lũy Mức Lệch Nhịp cho một số kẻ địch nhất định.</t>
         </is>
       </c>
     </row>
@@ -25895,7 +25895,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Một số đòn tấn công tích lũy Off-Tune Level cho một số kẻ địch nhất định</t>
+          <t>Một số đòn tấn công tích lũy Mức Lệch Nhịp cho một số kẻ địch nhất định.</t>
         </is>
       </c>
     </row>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Kẻ địch đạt Tối Đa Cấp Độ Lệch Nhịp sẽ bước vào trạng thái Mistune. Tấn công hoặc Dodge thành công để kích hoạt Tune Break.</t>
+          <t>Kẻ địch bước vào trạng thái Mistune ở cấp Off-Tune tối đa. Thực hiện tấn công hoặc né thành công để kích hoạt Tune Break.</t>
         </is>
       </c>
     </row>
@@ -26025,7 +26025,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Kẻ địch đạt Tối Đa Cấp Độ Lệch Nhịp sẽ bước vào trạng thái Mistune. Tấn công hoặc Dodge thành công để kích hoạt Tune Break.</t>
+          <t>Kẻ địch bước vào trạng thái Mistune ở cấp Off-Tune tối đa. Thực hiện tấn công hoặc né thành công để kích hoạt Tune Break.</t>
         </is>
       </c>
     </row>
@@ -26090,7 +26090,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Kẻ địch đạt Tối Đa Cấp Độ Lệch Nhịp sẽ bước vào trạng thái Mistune. Tấn công hoặc Dodge thành công để kích hoạt Tune Break.</t>
+          <t>Kẻ địch bước vào trạng thái Mistune ở cấp Off-Tune tối đa. Thực hiện tấn công hoặc né thành công để kích hoạt Tune Break.</t>
         </is>
       </c>
     </row>
@@ -26155,7 +26155,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Kẻ địch sẽ vào trạng thái Mistune khi sử dụng một số kỹ năng hoặc trong một số giai đoạn nhất định</t>
+          <t>Kẻ địch bước vào trạng thái Mistune khi sử dụng một số kỹ năng hoặc trong một số giai đoạn nhất định.</t>
         </is>
       </c>
     </row>
@@ -26220,7 +26220,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Kẻ địch sẽ vào trạng thái Mistune khi sử dụng một số kỹ năng hoặc trong một số giai đoạn nhất định</t>
+          <t>Kẻ địch bước vào trạng thái Mistune khi sử dụng một số kỹ năng hoặc trong một số giai đoạn nhất định.</t>
         </is>
       </c>
     </row>
@@ -26285,7 +26285,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Kẻ địch sẽ vào trạng thái Mistune khi sử dụng một số kỹ năng hoặc trong một số giai đoạn nhất định</t>
+          <t>Kẻ địch bước vào trạng thái Mistune khi sử dụng một số kỹ năng hoặc trong một số giai đoạn nhất định.</t>
         </is>
       </c>
     </row>
@@ -26350,7 +26350,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Một số kẻ địch sẽ ở trạng thái Khóa Status khi sử dụng kỹ năng niệm chú hoặc trong một số trạng thái nhất định. Trong thời gian này, Cấp Độ Lệ Nhịp không thể tích lũy và kẻ địch sẽ thoát khỏi trạng thái Mistune.</t>
+          <t>Một số kẻ địch sẽ ở trạng thái Khóa Trạng Thái khi sử dụng kỹ năng thi triển hoặc trong một số trạng thái nhất định. Trong thời gian này, Cấp Độ Lệ Âm không thể tích lũy và kẻ địch sẽ thoát khỏi trạng thái Lệ Âm.</t>
         </is>
       </c>
     </row>
@@ -26415,7 +26415,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Một số kẻ địch sẽ ở trạng thái Khóa Status khi sử dụng kỹ năng niệm chú hoặc trong một số trạng thái nhất định. Trong thời gian này, Cấp Độ Lệ Nhịp không thể tích lũy và kẻ địch sẽ thoát khỏi trạng thái Mistune.</t>
+          <t>Một số kẻ địch sẽ ở trạng thái Khóa Trạng Thái khi sử dụng kỹ năng thi triển hoặc trong một số trạng thái nhất định. Trong thời gian này, Cấp Độ Lệ Âm không thể tích lũy và kẻ địch sẽ thoát khỏi trạng thái Lệ Âm.</t>
         </is>
       </c>
     </row>
@@ -26480,7 +26480,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Một số kẻ địch sẽ ở trạng thái Khóa Status khi sử dụng kỹ năng niệm chú hoặc trong một số trạng thái nhất định. Trong thời gian này, Cấp Độ Lệ Nhịp không thể tích lũy và kẻ địch sẽ thoát khỏi trạng thái Mistune.</t>
+          <t>Một số kẻ địch sẽ ở trạng thái Khóa Trạng Thái khi sử dụng kỹ năng thi triển hoặc trong một số trạng thái nhất định. Trong thời gian này, Cấp Độ Lệ Âm không thể tích lũy và kẻ địch sẽ thoát khỏi trạng thái Lệ Âm.</t>
         </is>
       </c>
     </row>
@@ -26545,7 +26545,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Đã tìm thấy một vật phẩm mới trong bộ bài của bạn. Hãy chọn Transport Unit XE-01.</t>
+          <t>Đã phát hiện vật phẩm mới trong bộ bài của cậu. Hãy chọn Đơn vị Vận chuyển XE-01.</t>
         </is>
       </c>
     </row>
@@ -26610,7 +26610,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Đã tìm thấy một vật phẩm mới trong bộ bài của bạn. Hãy chọn Transport Unit XE-01.</t>
+          <t>Đã phát hiện vật phẩm mới trong bộ bài của cậu. Hãy chọn Đơn vị Vận chuyển XE-01.</t>
         </is>
       </c>
     </row>
@@ -26675,7 +26675,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Đã tìm thấy một vật phẩm mới trong bộ bài của bạn. Hãy chọn Transport Unit XE-01.</t>
+          <t>Đã phát hiện vật phẩm mới trong bộ bài của cậu. Hãy chọn Đơn vị Vận chuyển XE-01.</t>
         </is>
       </c>
     </row>
@@ -26740,7 +26740,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào thẻ để thêm vào tay bài.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào thẻ bài để thêm vào tay bài.</t>
         </is>
       </c>
     </row>
@@ -26805,7 +26805,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào thẻ để thêm vào tay bài.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào thẻ bài để thêm vào tay bài.</t>
         </is>
       </c>
     </row>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào thẻ để thêm vào tay bài.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào thẻ bài để thêm vào tay bài.</t>
         </is>
       </c>
     </row>
@@ -26935,7 +26935,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Bạn cũng có thể sử dụng Domain.</t>
+          <t>Cậu cũng có thể sử dụng Miền.</t>
         </is>
       </c>
     </row>
@@ -27000,7 +27000,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>{0}Bạn can also use Domain.</t>
+          <t>Bạn cũng có thể dùng Lĩnh Vực.</t>
         </is>
       </c>
     </row>
@@ -27065,7 +27065,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Bạn cũng có thể sử dụng Domain.</t>
+          <t>Cậu cũng có thể sử dụng Miền.</t>
         </is>
       </c>
     </row>
@@ -27130,7 +27130,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} vào đây để mở giao diện xây dựng và tiếp tục dự án tái thiết Lahai-Roi</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để mở giao diện xây dựng và tiếp tục dự án tái thiết Lahai-Roi</t>
         </is>
       </c>
     </row>
@@ -27195,7 +27195,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} vào đây để mở giao diện xây dựng và tiếp tục dự án tái thiết Lahai-Roi</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để mở giao diện xây dựng và tiếp tục dự án tái thiết Lahai-Roi</t>
         </is>
       </c>
     </row>
@@ -27260,7 +27260,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} vào đây để mở giao diện xây dựng và tiếp tục dự án tái thiết Lahai-Roi</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để mở giao diện xây dựng và tiếp tục dự án tái thiết Lahai-Roi</t>
         </is>
       </c>
     </row>
@@ -27325,7 +27325,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ trong Operation: Frontier Renewal để tiến triển giai đoạn tái thiết</t>
+          <t>Hoàn thành nhiệm vụ trong Chiến Dịch: Tái Thiết Biên Cương để tiến tới giai đoạn tái thiết</t>
         </is>
       </c>
     </row>
@@ -27390,7 +27390,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ trong Operation: Frontier Renewal để tiến triển giai đoạn tái thiết</t>
+          <t>Hoàn thành nhiệm vụ trong Chiến Dịch: Tái Thiết Biên Cương để tiến tới giai đoạn tái thiết</t>
         </is>
       </c>
     </row>
@@ -27455,7 +27455,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ trong Operation: Frontier Renewal để tiến triển giai đoạn tái thiết</t>
+          <t>Hoàn thành nhiệm vụ trong Chiến Dịch: Tái Thiết Biên Cương để tiến tới giai đoạn tái thiết</t>
         </is>
       </c>
     </row>
@@ -27520,7 +27520,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem các tuyến đường cần xây dựng lại trong giao diện mạng lưới tuyến.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem các tuyến đường cần xây dựng lại trong giao diện mạng lưới.</t>
         </is>
       </c>
     </row>
@@ -27585,7 +27585,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem các tuyến đường cần xây dựng lại trong giao diện mạng lưới tuyến.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem các tuyến đường cần xây dựng lại trong giao diện mạng lưới.</t>
         </is>
       </c>
     </row>
@@ -27650,7 +27650,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xem các tuyến đường cần xây dựng lại trong giao diện mạng lưới tuyến.</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem các tuyến đường cần xây dựng lại trong giao diện mạng lưới.</t>
         </is>
       </c>
     </row>
@@ -27715,7 +27715,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Chọn tuyến đường để tái thiết</t>
+          <t>Chọn một con đường để xây dựng lại</t>
         </is>
       </c>
     </row>
@@ -27780,7 +27780,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Chọn tuyến đường để tái thiết</t>
+          <t>Chọn một con đường để xây dựng lại</t>
         </is>
       </c>
     </row>
@@ -27845,7 +27845,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Chọn tuyến đường để tái thiết</t>
+          <t>Chọn một con đường để xây dựng lại</t>
         </is>
       </c>
     </row>
@@ -27910,7 +27910,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} để đặt Route Constructor làm điểm đến</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để đặt Bộ Xây Dựng Tuyến làm điểm đến.</t>
         </is>
       </c>
     </row>
@@ -27975,7 +27975,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} để đặt Route Constructor làm điểm đến</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để đặt Bộ Xây Dựng Tuyến làm điểm đến.</t>
         </is>
       </c>
     </row>
@@ -28040,7 +28040,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} để đặt Route Constructor làm điểm đến</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để đặt Bộ Xây Dựng Tuyến làm điểm đến.</t>
         </is>
       </c>
     </row>
@@ -28105,7 +28105,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Xây dựng lại đường tăng Network Activity</t>
+          <t>Khôi phục đường sá làm tăng Hoạt động Mạng lưới</t>
         </is>
       </c>
     </row>
@@ -28170,7 +28170,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Xây dựng lại đường tăng Network Activity</t>
+          <t>Khôi phục đường sá làm tăng Hoạt động Mạng lưới</t>
         </is>
       </c>
     </row>
@@ -28235,7 +28235,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Xây dựng lại đường tăng Network Activity</t>
+          <t>Khôi phục đường sá làm tăng Hoạt động Mạng lưới</t>
         </is>
       </c>
     </row>
@@ -28300,7 +28300,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Đạt đến các mốc Activity nhất định sẽ thúc đẩy tiến độ xây dựng lại Spacetrek Observatory</t>
+          <t>Đạt các cột mốc Hoạt động nhất định sẽ thúc đẩy tiến độ xây dựng lại Đài Thiên Văn Spacetrek</t>
         </is>
       </c>
     </row>
@@ -28365,7 +28365,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Đạt đến các mốc Activity nhất định sẽ thúc đẩy tiến độ xây dựng lại Spacetrek Observatory</t>
+          <t>Đạt các cột mốc Hoạt động nhất định sẽ thúc đẩy tiến độ xây dựng lại Đài Thiên Văn Spacetrek</t>
         </is>
       </c>
     </row>
@@ -28430,7 +28430,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Đạt đến các mốc Activity nhất định sẽ thúc đẩy tiến độ xây dựng lại Spacetrek Observatory</t>
+          <t>Đạt các cột mốc Hoạt động nhất định sẽ thúc đẩy tiến độ xây dựng lại Đài Thiên Văn Spacetrek</t>
         </is>
       </c>
     </row>
@@ -28495,7 +28495,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Bạn sẽ nhận được lời cảm ơn từ Spacetrek Collective sau khi xây dựng lại mạng lưới tuyến đường</t>
+          <t>Bạn sẽ nhận được lời cảm ơn từ Spacetrek Collective sau khi khôi phục mạng lưới tuyến đường.</t>
         </is>
       </c>
     </row>
@@ -28560,7 +28560,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Bạn sẽ nhận được lời cảm ơn từ Spacetrek Collective sau khi xây dựng lại mạng lưới tuyến đường</t>
+          <t>Bạn sẽ nhận được lời cảm ơn từ Spacetrek Collective sau khi khôi phục mạng lưới tuyến đường.</t>
         </is>
       </c>
     </row>
@@ -28625,7 +28625,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Bạn sẽ nhận được lời cảm ơn từ Spacetrek Collective sau khi xây dựng lại mạng lưới tuyến đường</t>
+          <t>Bạn sẽ nhận được lời cảm ơn từ Spacetrek Collective sau khi khôi phục mạng lưới tuyến đường.</t>
         </is>
       </c>
     </row>
@@ -28690,7 +28690,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem Spacetrek Observatory Files</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Hồ Sơ Đài Quan Sát Spacetrek.</t>
         </is>
       </c>
     </row>
@@ -28755,7 +28755,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem Spacetrek Observatory Files</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Hồ Sơ Đài Quan Sát Spacetrek.</t>
         </is>
       </c>
     </row>
@@ -28820,7 +28820,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem Spacetrek Observatory Files</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem Hồ Sơ Đài Quan Sát Spacetrek.</t>
         </is>
       </c>
     </row>
@@ -28885,7 +28885,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Các tài liệu liên quan đến Spacetrek Observatory có thể được tìm thấy trên khắp Lahai-Roi</t>
+          <t>Có thể tìm thấy các hồ sơ liên quan đến Đài quan sát Spacetrek rải rác khắp Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -28950,7 +28950,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Các tài liệu liên quan đến Spacetrek Observatory có thể được tìm thấy trên khắp Lahai-Roi</t>
+          <t>Có thể tìm thấy các hồ sơ liên quan đến Đài quan sát Spacetrek rải rác khắp Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -29015,7 +29015,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Các tài liệu liên quan đến Spacetrek Observatory có thể được tìm thấy trên khắp Lahai-Roi</t>
+          <t>Có thể tìm thấy các hồ sơ liên quan đến Đài quan sát Spacetrek rải rác khắp Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -29080,7 +29080,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để chọn thời tiết muốn mô phỏng</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chọn kiểu thời tiết muốn mô phỏng</t>
         </is>
       </c>
     </row>
@@ -29145,7 +29145,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để chọn thời tiết muốn mô phỏng</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chọn kiểu thời tiết muốn mô phỏng</t>
         </is>
       </c>
     </row>
@@ -29210,7 +29210,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press} vào đây để chọn thời tiết muốn mô phỏng</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để chọn kiểu thời tiết muốn mô phỏng</t>
         </is>
       </c>
     </row>
@@ -29275,7 +29275,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Thời gian sẽ tự động điều chỉnh để đáp ứng yêu cầu của Weather Simulation nếu cần</t>
+          <t>Thời gian sẽ tự động điều chỉnh để đáp ứng yêu cầu Mô Phỏng Thời Tiết nếu cần</t>
         </is>
       </c>
     </row>
@@ -29340,7 +29340,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Thời gian sẽ tự động điều chỉnh để đáp ứng yêu cầu của Weather Simulation nếu cần</t>
+          <t>Thời gian sẽ tự động điều chỉnh để đáp ứng yêu cầu Mô Phỏng Thời Tiết nếu cần</t>
         </is>
       </c>
     </row>
@@ -29405,7 +29405,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Thời gian sẽ tự động điều chỉnh để đáp ứng yêu cầu của Weather Simulation nếu cần</t>
+          <t>Thời gian sẽ tự động điều chỉnh để đáp ứng yêu cầu Mô Phỏng Thời Tiết nếu cần</t>
         </is>
       </c>
     </row>
@@ -29470,7 +29470,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xác nhận Weather Simulation.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xác nhận Mô Phỏng Thời Tiết.</t>
         </is>
       </c>
     </row>
@@ -29535,7 +29535,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xác nhận Weather Simulation.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xác nhận Mô Phỏng Thời Tiết.</t>
         </is>
       </c>
     </row>
@@ -29600,7 +29600,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} vào đây để xác nhận Weather Simulation.</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} vào đây để xác nhận Mô Phỏng Thời Tiết.</t>
         </is>
       </c>
     </row>
@@ -29665,7 +29665,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem kết quả xây dựng trong giao diện mạng lộ trình</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem kết quả xây dựng trong giao diện mạng lưới tuyến đường.</t>
         </is>
       </c>
     </row>
@@ -29730,7 +29730,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem kết quả xây dựng trong giao diện mạng lộ trình</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem kết quả xây dựng trong giao diện mạng lưới tuyến đường.</t>
         </is>
       </c>
     </row>
@@ -29795,7 +29795,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=click Gamepad=press} để xem kết quả xây dựng trong giao diện mạng lộ trình</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem kết quả xây dựng trong giao diện mạng lưới tuyến đường.</t>
         </is>
       </c>
     </row>
@@ -29860,7 +29860,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>{0} Dùng Projector để tạo Echo Projection cho các tương tác đặc biệt</t>
+          <t>Sử dụng Projector để tạo Echo Projection cho các tương tác đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -29925,7 +29925,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Dùng Máy Chiếu để tạo Hình Ảnh Echo phục vụ các tương tác đặc biệt</t>
+          <t>Dùng Máy Chiếu để tạo ra Echo Projection phục vụ các tương tác đặc biệt</t>
         </is>
       </c>
     </row>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Edit Echoes đã trang bị trong Projector tại đây</t>
+          <t>Chỉnh sửa Echo đã trang bị trong Máy chiếu tại đây</t>
         </is>
       </c>
     </row>
@@ -30055,7 +30055,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Edit Echoes đã trang bị trong Projector tại đây</t>
+          <t>Chỉnh sửa Echo đã trang bị trong Máy chiếu tại đây</t>
         </is>
       </c>
     </row>
@@ -30120,7 +30120,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Edit Echoes đã trang bị trong Projector tại đây</t>
+          <t>Chỉnh sửa Echo đã trang bị trong Máy chiếu tại đây</t>
         </is>
       </c>
     </row>
@@ -30185,7 +30185,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Equip Echoes có sẵn để chiếu tại đây</t>
+          <t>Gắn Echo có sẵn để chiếu tại đây</t>
         </is>
       </c>
     </row>
@@ -30250,7 +30250,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Equip Echoes có sẵn để chiếu tại đây</t>
+          <t>Gắn Echo có sẵn để chiếu tại đây</t>
         </is>
       </c>
     </row>
@@ -30315,7 +30315,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Equip Echoes có sẵn để chiếu tại đây</t>
+          <t>Gắn Echo có sẵn để chiếu tại đây</t>
         </is>
       </c>
     </row>
@@ -30380,7 +30380,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Bạn có thể chiếu Echoes đã trang bị thông qua Công cụ: Máy chiếu</t>
+          <t>Bạn có thể chiếu Echo đã trang bị thông qua Tiện ích: Máy chiếu.</t>
         </is>
       </c>
     </row>
@@ -30445,7 +30445,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Bạn có thể chiếu Echoes đã trang bị thông qua Công cụ: Máy chiếu</t>
+          <t>Bạn có thể chiếu Echo đã trang bị thông qua Tiện ích: Máy chiếu.</t>
         </is>
       </c>
     </row>
@@ -30510,7 +30510,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Bạn có thể chiếu Echoes đã trang bị thông qua Công cụ: Máy chiếu</t>
+          <t>Bạn có thể chiếu Echo đã trang bị thông qua Tiện ích: Máy chiếu.</t>
         </is>
       </c>
     </row>
@@ -30575,7 +30575,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Một số Resonators có thể chuyển đổi giữa các Modes Resonance và thay đổi đặc tính chiến đấu.</t>
+          <t>Một số Resonator có thể chuyển đổi giữa các Chế Độ Cộng Hưởng và thay đổi đặc tính chiến đấu của mình.</t>
         </is>
       </c>
     </row>
@@ -30640,7 +30640,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Một số Resonators có thể chuyển đổi giữa các Modes Resonance và thay đổi đặc tính chiến đấu.</t>
+          <t>Một số Resonator có thể chuyển đổi giữa các Chế Độ Cộng Hưởng và thay đổi đặc tính chiến đấu của mình.</t>
         </is>
       </c>
     </row>
@@ -30705,7 +30705,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Một số Resonators có thể chuyển đổi giữa các Modes Resonance và thay đổi đặc tính chiến đấu.</t>
+          <t>Một số Resonator có thể chuyển đổi giữa các Chế Độ Cộng Hưởng và thay đổi đặc tính chiến đấu của mình.</t>
         </is>
       </c>
     </row>
@@ -30770,7 +30770,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Một số kỹ năng sẽ có hiệu ứng khác nhau dựa trên Chế độ Cộng hưởng</t>
+          <t>Một số kỹ năng sẽ có hiệu ứng khác nhau tùy vào Chế Độ Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -30835,7 +30835,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Một số kỹ năng sẽ có hiệu ứng khác nhau dựa trên Chế độ Cộng hưởng</t>
+          <t>Một số kỹ năng sẽ có hiệu ứng khác nhau tùy vào Chế Độ Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -30900,7 +30900,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Một số kỹ năng sẽ có hiệu ứng khác nhau dựa trên Chế độ Cộng hưởng</t>
+          <t>Một số kỹ năng sẽ có hiệu ứng khác nhau tùy vào Chế Độ Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -30965,7 +30965,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} vào đây để xem chi tiết Resonance Mode</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết Chế Độ Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -31030,7 +31030,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} vào đây để xem chi tiết Resonance Mode</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết Chế Độ Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -31095,7 +31095,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=press} vào đây để xem chi tiết Resonance Mode</t>
+          <t>Nhấn {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} để xem chi tiết Chế Độ Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -31160,7 +31160,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Giữ {0} để Xuống Thú nhanh và thực hiện Attack Xuống Thú</t>
+          <t>Giữ {0} để Xuống Thú nhanh và thực hiện Đòn Hạ Thú</t>
         </is>
       </c>
     </row>
@@ -31225,7 +31225,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Giữ {0} để Xuống Thú nhanh và thực hiện Attack Xuống Thú</t>
+          <t>Giữ {0} để Xuống Thú nhanh và thực hiện Đòn Hạ Thú</t>
         </is>
       </c>
     </row>
@@ -31290,7 +31290,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Giữ để Xuống Thú nhanh và thực hiện Đòn Xuống Thú</t>
+          <t>Giữ để Xuống Thú nhanh và thực hiện Tấn Công Xuống Thú</t>
         </is>
       </c>
     </row>
@@ -31355,7 +31355,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} để nhảy lên lan can và trượt.</t>
+          <t>Nhấn để nhảy lên đường ray và trượt.</t>
         </is>
       </c>
     </row>
@@ -31420,7 +31420,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} để nhảy lên lan can và trượt.</t>
+          <t>Nhấn để nhảy lên đường ray và trượt.</t>
         </is>
       </c>
     </row>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Đường đua hiện tại hiển thị tại đây.</t>
+          <t>Đường đua hiện tại được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -31550,7 +31550,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Đường đua hiện tại hiển thị tại đây.</t>
+          <t>Đường đua hiện tại được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -31615,7 +31615,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Đường đua hiện tại hiển thị tại đây.</t>
+          <t>Đường đua hiện tại được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -31680,7 +31680,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Vượt kỷ lục đua trên bảng xếp hạng để nhận thưởng</t>
+          <t>Phá kỷ lục đua trên bảng xếp hạng để nhận thưởng</t>
         </is>
       </c>
     </row>
@@ -31745,7 +31745,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Vượt kỷ lục đua trên bảng xếp hạng để nhận thưởng</t>
+          <t>Phá kỷ lục đua trên bảng xếp hạng để nhận thưởng</t>
         </is>
       </c>
     </row>
@@ -31810,7 +31810,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Vượt kỷ lục đua trên bảng xếp hạng để nhận thưởng</t>
+          <t>Phá kỷ lục đua trên bảng xếp hạng để nhận thưởng</t>
         </is>
       </c>
     </row>
@@ -31875,7 +31875,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Bản đồ đường đua được hiển thị tại đây. Điểm sáng đại diện cho vị trí hiện tại của cậu.</t>
+          <t>Bản đồ trường đua được hiển thị tại đây. Chấm sáng đại diện cho vị trí hiện tại của cậu.</t>
         </is>
       </c>
     </row>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Bản đồ đường đua được hiển thị tại đây. Điểm sáng đại diện cho vị trí hiện tại của cậu.</t>
+          <t>Bản đồ trường đua được hiển thị tại đây. Chấm sáng đại diện cho vị trí hiện tại của cậu.</t>
         </is>
       </c>
     </row>
@@ -32005,7 +32005,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Bản đồ đường đua được hiển thị tại đây. Điểm sáng đại diện cho vị trí hiện tại của cậu.</t>
+          <t>Bản đồ trường đua được hiển thị tại đây. Chấm sáng đại diện cho vị trí hiện tại của cậu.</t>
         </is>
       </c>
     </row>
@@ -32070,7 +32070,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Finish số vòng đua quy định để hoàn tất đường đua</t>
+          <t>Hoàn thành đủ số vòng đua để vượt qua đường đua</t>
         </is>
       </c>
     </row>
@@ -32135,7 +32135,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Finish số vòng đua quy định để hoàn tất đường đua</t>
+          <t>Hoàn thành đủ số vòng đua để vượt qua đường đua</t>
         </is>
       </c>
     </row>
@@ -32200,7 +32200,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Finish số vòng đua quy định để hoàn tất đường đua</t>
+          <t>Hoàn thành đủ số vòng đua để vượt qua đường đua</t>
         </is>
       </c>
     </row>
@@ -32265,7 +32265,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để tham gia Stability Accords.</t>
+          <t>Nhấn vào đây để tham gia Hiệp Ước Ổn Định.</t>
         </is>
       </c>
     </row>
@@ -32330,7 +32330,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để tham gia Stability Accords.</t>
+          <t>Nhấn vào đây để tham gia Hiệp Ước Ổn Định.</t>
         </is>
       </c>
     </row>
@@ -32395,7 +32395,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=Bấm Gamepad=press} vào đây để tham gia Stability Accords.</t>
+          <t>Nhấn vào đây để tham gia Hiệp Ước Ổn Định.</t>
         </is>
       </c>
     </row>
@@ -32460,7 +32460,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Danh sách kẻ địch hiển thị tại đây và sẽ xuất hiện theo thứ tự như đã liệt kê.</t>
+          <t>Danh sách kẻ địch sẽ hiển thị tại đây và xuất hiện theo thứ tự đã sắp xếp.</t>
         </is>
       </c>
     </row>
@@ -32525,7 +32525,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Danh sách kẻ địch hiển thị tại đây và sẽ xuất hiện theo thứ tự như đã liệt kê.</t>
+          <t>Danh sách kẻ địch sẽ hiển thị tại đây và xuất hiện theo thứ tự đã sắp xếp.</t>
         </is>
       </c>
     </row>
@@ -32590,7 +32590,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Danh sách kẻ địch hiển thị tại đây và sẽ xuất hiện theo thứ tự như đã liệt kê.</t>
+          <t>Danh sách kẻ địch sẽ hiển thị tại đây và xuất hiện theo thứ tự đã sắp xếp.</t>
         </is>
       </c>
     </row>
@@ -32655,7 +32655,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Chọn Power Circuit tại đây. Power Circuit sẽ được áp dụng cho đội hiện tại.</t>
+          <t>Chọn Mạch Năng Lượng tại đây. Mạch Năng Lượng sẽ được áp dụng cho đội hiện tại.</t>
         </is>
       </c>
     </row>
@@ -32720,7 +32720,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Chọn Power Circuit tại đây. Power Circuit sẽ được áp dụng cho đội hiện tại.</t>
+          <t>Chọn Mạch Năng Lượng tại đây. Mạch Năng Lượng sẽ được áp dụng cho đội hiện tại.</t>
         </is>
       </c>
     </row>
@@ -32785,7 +32785,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Chọn Power Circuit tại đây. Power Circuit sẽ được áp dụng cho đội hiện tại.</t>
+          <t>Chọn Mạch Năng Lượng tại đây. Mạch Năng Lượng sẽ được áp dụng cho đội hiện tại.</t>
         </is>
       </c>
     </row>
@@ -32850,7 +32850,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Các Demo Resonators có thể tìm thấy tại đây và chỉ có thể mở khóa nếu bạn sở hữu Resonators tương ứng.</t>
+          <t>Resonator demo có thể tìm thấy tại đây, và chỉ mở khóa được nếu bạn sở hữu Resonator tương ứng.</t>
         </is>
       </c>
     </row>
@@ -32915,7 +32915,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Các Demo Resonators có thể tìm thấy tại đây và chỉ có thể mở khóa nếu bạn sở hữu Resonators tương ứng.</t>
+          <t>Resonator demo có thể tìm thấy tại đây, và chỉ mở khóa được nếu bạn sở hữu Resonator tương ứng.</t>
         </is>
       </c>
     </row>
@@ -32980,7 +32980,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Các Demo Resonators có thể tìm thấy tại đây và chỉ có thể mở khóa nếu bạn sở hữu Resonators tương ứng.</t>
+          <t>Resonator demo có thể tìm thấy tại đây, và chỉ mở khóa được nếu bạn sở hữu Resonator tương ứng.</t>
         </is>
       </c>
     </row>
@@ -33045,7 +33045,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>HP của kẻ địch bất bại không reset khi đối mặt với đội hình mới.</t>
+          <t>Kẻ địch bất bại sẽ không hồi phục HP khi đối mặt với đội hình mới.</t>
         </is>
       </c>
     </row>
